--- a/Shared/DocumentsValidationData/Passing/8XXX_Cause and Effect Matrix_R0.0_ValidationTemplate.xlsx
+++ b/Shared/DocumentsValidationData/Passing/8XXX_Cause and Effect Matrix_R0.0_ValidationTemplate.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Source\Repos\Openn2\Excel Resources\3_Database\Source Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Source\Repos\_Openn2\Shared\DocumentsValidationData\Passing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86155963-E6FC-4A5A-8206-584B66E0EEC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C2ABE88-CE84-4A08-8E04-7137F7AE5F28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17790" tabRatio="713" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17790" tabRatio="713" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COVER" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="204">
   <si>
     <t>PROJECT ID</t>
   </si>
@@ -645,9 +645,6 @@
     <t>-S67002</t>
   </si>
   <si>
-    <t>EMERGENCY 'RESET</t>
-  </si>
-  <si>
     <t>'Interlocked Safety Switch</t>
   </si>
   <si>
@@ -703,10 +700,6 @@
   </si>
   <si>
     <t>First Emission Validation Template</t>
-  </si>
-  <si>
-    <t>Area 2
-(Conveyors)</t>
   </si>
   <si>
     <t>Emergency from external machine cause power cut off of machine according to the matrix</t>
@@ -758,12 +751,132 @@
   <si>
     <t>-X80101</t>
   </si>
+  <si>
+    <t>=S1+PC1.CC1-Q80001</t>
+  </si>
+  <si>
+    <t>Q140.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEST </t>
+  </si>
+  <si>
+    <t>EMERGENCY RESET</t>
+  </si>
+  <si>
+    <t>I20.6</t>
+  </si>
+  <si>
+    <t>-S67008</t>
+  </si>
+  <si>
+    <t>I20.3</t>
+  </si>
+  <si>
+    <t>4/12</t>
+  </si>
+  <si>
+    <t>FIRE ALARM</t>
+  </si>
+  <si>
+    <t>-X40001</t>
+  </si>
+  <si>
+    <t>=S2+DU01.CC1, =S2+DU02.CC1, =S2+DU03.CC1, =S2+DU10.CC1</t>
+  </si>
+  <si>
+    <t>=S2+PC2.CC1-Q66401..2</t>
+  </si>
+  <si>
+    <t>=S2+PC2.CC1-X80201</t>
+  </si>
+  <si>
+    <t>Q1130.0</t>
+  </si>
+  <si>
+    <t>Q1130.1</t>
+  </si>
+  <si>
+    <t>=S2+MA2.CC2</t>
+  </si>
+  <si>
+    <t>=S2+PC2.CC1-Q80001</t>
+  </si>
+  <si>
+    <t>Q1140.0</t>
+  </si>
+  <si>
+    <t>=S1+PC2.CC1</t>
+  </si>
+  <si>
+    <t>=S1+MS2.CC1</t>
+  </si>
+  <si>
+    <t>I1020.0</t>
+  </si>
+  <si>
+    <t>I1020.1</t>
+  </si>
+  <si>
+    <t>I1120.0</t>
+  </si>
+  <si>
+    <t>I1120.2</t>
+  </si>
+  <si>
+    <t>I1110.0</t>
+  </si>
+  <si>
+    <t>I1020.2</t>
+  </si>
+  <si>
+    <t>I1020.6</t>
+  </si>
+  <si>
+    <t>I1020.3</t>
+  </si>
+  <si>
+    <t>=S2</t>
+  </si>
+  <si>
+    <t>+SG3</t>
+  </si>
+  <si>
+    <t>+SG4</t>
+  </si>
+  <si>
+    <t>+MS2.CC1</t>
+  </si>
+  <si>
+    <t>+PC2.CC1</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>AREA 3</t>
+  </si>
+  <si>
+    <t>AREA 4</t>
+  </si>
+  <si>
+    <t>Area 2
+(Conveyors East)</t>
+  </si>
+  <si>
+    <t>Area 2
+(Conveyors West)</t>
+  </si>
+  <si>
+    <t>Area 2
+(Conveyors North)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="52" x14ac:knownFonts="1">
+  <fonts count="53" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1143,6 +1256,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -2164,7 +2283,7 @@
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="332">
+  <cellXfs count="344">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2446,6 +2565,42 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="52" fillId="0" borderId="0" xfId="7" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="52" fillId="8" borderId="0" xfId="7" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3128,7 +3283,49 @@
     <cellStyle name="Normal 6" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
     <cellStyle name="Normal 7" xfId="7" xr:uid="{94404F9A-2A3A-4334-8C11-5333B864236F}"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="14">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <color theme="0"/>
@@ -3889,279 +4086,279 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="186"/>
-      <c r="B1" s="187"/>
-      <c r="C1" s="187"/>
-      <c r="D1" s="187"/>
-      <c r="E1" s="187"/>
-      <c r="F1" s="187"/>
-      <c r="G1" s="187"/>
-      <c r="H1" s="187"/>
-      <c r="I1" s="187"/>
-      <c r="J1" s="187"/>
-      <c r="K1" s="187"/>
-      <c r="L1" s="188"/>
+      <c r="A1" s="198"/>
+      <c r="B1" s="199"/>
+      <c r="C1" s="199"/>
+      <c r="D1" s="199"/>
+      <c r="E1" s="199"/>
+      <c r="F1" s="199"/>
+      <c r="G1" s="199"/>
+      <c r="H1" s="199"/>
+      <c r="I1" s="199"/>
+      <c r="J1" s="199"/>
+      <c r="K1" s="199"/>
+      <c r="L1" s="200"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="189"/>
-      <c r="B2" s="164"/>
-      <c r="C2" s="164"/>
-      <c r="D2" s="164"/>
-      <c r="E2" s="164"/>
-      <c r="F2" s="164"/>
-      <c r="G2" s="164"/>
-      <c r="H2" s="164"/>
-      <c r="I2" s="164"/>
-      <c r="J2" s="164"/>
-      <c r="K2" s="164"/>
-      <c r="L2" s="167"/>
+      <c r="A2" s="201"/>
+      <c r="B2" s="176"/>
+      <c r="C2" s="176"/>
+      <c r="D2" s="176"/>
+      <c r="E2" s="176"/>
+      <c r="F2" s="176"/>
+      <c r="G2" s="176"/>
+      <c r="H2" s="176"/>
+      <c r="I2" s="176"/>
+      <c r="J2" s="176"/>
+      <c r="K2" s="176"/>
+      <c r="L2" s="179"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="189"/>
-      <c r="B3" s="164"/>
-      <c r="C3" s="164"/>
-      <c r="D3" s="164"/>
-      <c r="E3" s="164"/>
-      <c r="F3" s="164"/>
-      <c r="G3" s="164"/>
-      <c r="H3" s="164"/>
-      <c r="I3" s="164"/>
-      <c r="J3" s="164"/>
-      <c r="K3" s="164"/>
-      <c r="L3" s="167"/>
+      <c r="A3" s="201"/>
+      <c r="B3" s="176"/>
+      <c r="C3" s="176"/>
+      <c r="D3" s="176"/>
+      <c r="E3" s="176"/>
+      <c r="F3" s="176"/>
+      <c r="G3" s="176"/>
+      <c r="H3" s="176"/>
+      <c r="I3" s="176"/>
+      <c r="J3" s="176"/>
+      <c r="K3" s="176"/>
+      <c r="L3" s="179"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="189"/>
-      <c r="B4" s="164"/>
-      <c r="C4" s="164"/>
-      <c r="D4" s="164"/>
-      <c r="E4" s="164"/>
-      <c r="F4" s="164"/>
-      <c r="G4" s="164"/>
-      <c r="H4" s="164"/>
-      <c r="I4" s="164"/>
-      <c r="J4" s="164"/>
-      <c r="K4" s="164"/>
-      <c r="L4" s="167"/>
+      <c r="A4" s="201"/>
+      <c r="B4" s="176"/>
+      <c r="C4" s="176"/>
+      <c r="D4" s="176"/>
+      <c r="E4" s="176"/>
+      <c r="F4" s="176"/>
+      <c r="G4" s="176"/>
+      <c r="H4" s="176"/>
+      <c r="I4" s="176"/>
+      <c r="J4" s="176"/>
+      <c r="K4" s="176"/>
+      <c r="L4" s="179"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="189"/>
-      <c r="B5" s="164"/>
-      <c r="C5" s="164"/>
-      <c r="D5" s="164"/>
-      <c r="E5" s="164"/>
-      <c r="F5" s="164"/>
-      <c r="G5" s="164"/>
-      <c r="H5" s="164"/>
-      <c r="I5" s="164"/>
-      <c r="J5" s="164"/>
-      <c r="K5" s="164"/>
-      <c r="L5" s="167"/>
+      <c r="A5" s="201"/>
+      <c r="B5" s="176"/>
+      <c r="C5" s="176"/>
+      <c r="D5" s="176"/>
+      <c r="E5" s="176"/>
+      <c r="F5" s="176"/>
+      <c r="G5" s="176"/>
+      <c r="H5" s="176"/>
+      <c r="I5" s="176"/>
+      <c r="J5" s="176"/>
+      <c r="K5" s="176"/>
+      <c r="L5" s="179"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="189"/>
-      <c r="B6" s="164"/>
-      <c r="C6" s="164"/>
-      <c r="D6" s="164"/>
-      <c r="E6" s="164"/>
-      <c r="F6" s="164"/>
-      <c r="G6" s="164"/>
-      <c r="H6" s="164"/>
-      <c r="I6" s="164"/>
-      <c r="J6" s="164"/>
-      <c r="K6" s="164"/>
-      <c r="L6" s="167"/>
+      <c r="A6" s="201"/>
+      <c r="B6" s="176"/>
+      <c r="C6" s="176"/>
+      <c r="D6" s="176"/>
+      <c r="E6" s="176"/>
+      <c r="F6" s="176"/>
+      <c r="G6" s="176"/>
+      <c r="H6" s="176"/>
+      <c r="I6" s="176"/>
+      <c r="J6" s="176"/>
+      <c r="K6" s="176"/>
+      <c r="L6" s="179"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="189"/>
-      <c r="B7" s="164"/>
-      <c r="C7" s="164"/>
-      <c r="D7" s="164"/>
-      <c r="E7" s="164"/>
-      <c r="F7" s="164"/>
-      <c r="G7" s="164"/>
-      <c r="H7" s="164"/>
-      <c r="I7" s="164"/>
-      <c r="J7" s="164"/>
-      <c r="K7" s="164"/>
-      <c r="L7" s="167"/>
+      <c r="A7" s="201"/>
+      <c r="B7" s="176"/>
+      <c r="C7" s="176"/>
+      <c r="D7" s="176"/>
+      <c r="E7" s="176"/>
+      <c r="F7" s="176"/>
+      <c r="G7" s="176"/>
+      <c r="H7" s="176"/>
+      <c r="I7" s="176"/>
+      <c r="J7" s="176"/>
+      <c r="K7" s="176"/>
+      <c r="L7" s="179"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="189"/>
-      <c r="B8" s="164"/>
-      <c r="C8" s="164"/>
-      <c r="D8" s="164"/>
-      <c r="E8" s="164"/>
-      <c r="F8" s="164"/>
-      <c r="G8" s="164"/>
-      <c r="H8" s="164"/>
-      <c r="I8" s="164"/>
-      <c r="J8" s="164"/>
-      <c r="K8" s="164"/>
-      <c r="L8" s="167"/>
+      <c r="A8" s="201"/>
+      <c r="B8" s="176"/>
+      <c r="C8" s="176"/>
+      <c r="D8" s="176"/>
+      <c r="E8" s="176"/>
+      <c r="F8" s="176"/>
+      <c r="G8" s="176"/>
+      <c r="H8" s="176"/>
+      <c r="I8" s="176"/>
+      <c r="J8" s="176"/>
+      <c r="K8" s="176"/>
+      <c r="L8" s="179"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="189"/>
-      <c r="B9" s="164"/>
-      <c r="C9" s="164"/>
-      <c r="D9" s="164"/>
-      <c r="E9" s="164"/>
-      <c r="F9" s="164"/>
-      <c r="G9" s="164"/>
-      <c r="H9" s="164"/>
-      <c r="I9" s="164"/>
-      <c r="J9" s="164"/>
-      <c r="K9" s="164"/>
-      <c r="L9" s="167"/>
+      <c r="A9" s="201"/>
+      <c r="B9" s="176"/>
+      <c r="C9" s="176"/>
+      <c r="D9" s="176"/>
+      <c r="E9" s="176"/>
+      <c r="F9" s="176"/>
+      <c r="G9" s="176"/>
+      <c r="H9" s="176"/>
+      <c r="I9" s="176"/>
+      <c r="J9" s="176"/>
+      <c r="K9" s="176"/>
+      <c r="L9" s="179"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="189"/>
-      <c r="B10" s="164"/>
-      <c r="C10" s="164"/>
-      <c r="D10" s="164"/>
-      <c r="E10" s="164"/>
-      <c r="F10" s="164"/>
-      <c r="G10" s="164"/>
-      <c r="H10" s="164"/>
-      <c r="I10" s="164"/>
-      <c r="J10" s="164"/>
-      <c r="K10" s="164"/>
-      <c r="L10" s="167"/>
+      <c r="A10" s="201"/>
+      <c r="B10" s="176"/>
+      <c r="C10" s="176"/>
+      <c r="D10" s="176"/>
+      <c r="E10" s="176"/>
+      <c r="F10" s="176"/>
+      <c r="G10" s="176"/>
+      <c r="H10" s="176"/>
+      <c r="I10" s="176"/>
+      <c r="J10" s="176"/>
+      <c r="K10" s="176"/>
+      <c r="L10" s="179"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="189"/>
-      <c r="B11" s="164"/>
-      <c r="C11" s="164"/>
-      <c r="D11" s="164"/>
-      <c r="E11" s="164"/>
-      <c r="F11" s="164"/>
-      <c r="G11" s="164"/>
-      <c r="H11" s="164"/>
-      <c r="I11" s="164"/>
-      <c r="J11" s="164"/>
-      <c r="K11" s="164"/>
-      <c r="L11" s="167"/>
+      <c r="A11" s="201"/>
+      <c r="B11" s="176"/>
+      <c r="C11" s="176"/>
+      <c r="D11" s="176"/>
+      <c r="E11" s="176"/>
+      <c r="F11" s="176"/>
+      <c r="G11" s="176"/>
+      <c r="H11" s="176"/>
+      <c r="I11" s="176"/>
+      <c r="J11" s="176"/>
+      <c r="K11" s="176"/>
+      <c r="L11" s="179"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="190" t="s">
+      <c r="A12" s="202" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="191"/>
-      <c r="C12" s="191"/>
-      <c r="D12" s="191"/>
-      <c r="E12" s="191"/>
-      <c r="F12" s="191"/>
-      <c r="G12" s="191"/>
-      <c r="H12" s="191"/>
-      <c r="I12" s="191"/>
-      <c r="J12" s="191"/>
-      <c r="K12" s="191"/>
-      <c r="L12" s="192"/>
+      <c r="B12" s="203"/>
+      <c r="C12" s="203"/>
+      <c r="D12" s="203"/>
+      <c r="E12" s="203"/>
+      <c r="F12" s="203"/>
+      <c r="G12" s="203"/>
+      <c r="H12" s="203"/>
+      <c r="I12" s="203"/>
+      <c r="J12" s="203"/>
+      <c r="K12" s="203"/>
+      <c r="L12" s="204"/>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="193"/>
-      <c r="B13" s="194"/>
-      <c r="C13" s="194"/>
-      <c r="D13" s="194"/>
-      <c r="E13" s="194"/>
-      <c r="F13" s="194"/>
-      <c r="G13" s="194"/>
-      <c r="H13" s="194"/>
-      <c r="I13" s="194"/>
-      <c r="J13" s="194"/>
-      <c r="K13" s="194"/>
-      <c r="L13" s="195"/>
+      <c r="A13" s="205"/>
+      <c r="B13" s="206"/>
+      <c r="C13" s="206"/>
+      <c r="D13" s="206"/>
+      <c r="E13" s="206"/>
+      <c r="F13" s="206"/>
+      <c r="G13" s="206"/>
+      <c r="H13" s="206"/>
+      <c r="I13" s="206"/>
+      <c r="J13" s="206"/>
+      <c r="K13" s="206"/>
+      <c r="L13" s="207"/>
     </row>
     <row r="14" spans="1:20" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="196" t="s">
+      <c r="A14" s="208" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="197"/>
-      <c r="C14" s="200" t="s">
+      <c r="B14" s="209"/>
+      <c r="C14" s="212" t="s">
+        <v>153</v>
+      </c>
+      <c r="D14" s="212"/>
+      <c r="E14" s="212"/>
+      <c r="F14" s="217" t="s">
+        <v>0</v>
+      </c>
+      <c r="G14" s="218"/>
+      <c r="H14" s="218"/>
+      <c r="I14" s="218"/>
+      <c r="J14" s="219"/>
+      <c r="K14" s="223" t="s">
         <v>154</v>
       </c>
-      <c r="D14" s="200"/>
-      <c r="E14" s="200"/>
-      <c r="F14" s="205" t="s">
-        <v>0</v>
-      </c>
-      <c r="G14" s="206"/>
-      <c r="H14" s="206"/>
-      <c r="I14" s="206"/>
-      <c r="J14" s="207"/>
-      <c r="K14" s="211" t="s">
-        <v>155</v>
-      </c>
-      <c r="L14" s="212"/>
+      <c r="L14" s="224"/>
     </row>
     <row r="15" spans="1:20" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="198"/>
-      <c r="B15" s="199"/>
-      <c r="C15" s="200"/>
-      <c r="D15" s="200"/>
-      <c r="E15" s="200"/>
-      <c r="F15" s="208"/>
-      <c r="G15" s="209"/>
-      <c r="H15" s="209"/>
-      <c r="I15" s="209"/>
-      <c r="J15" s="210"/>
-      <c r="K15" s="213"/>
-      <c r="L15" s="214"/>
+      <c r="A15" s="210"/>
+      <c r="B15" s="211"/>
+      <c r="C15" s="212"/>
+      <c r="D15" s="212"/>
+      <c r="E15" s="212"/>
+      <c r="F15" s="220"/>
+      <c r="G15" s="221"/>
+      <c r="H15" s="221"/>
+      <c r="I15" s="221"/>
+      <c r="J15" s="222"/>
+      <c r="K15" s="225"/>
+      <c r="L15" s="226"/>
       <c r="T15" s="4"/>
     </row>
     <row r="16" spans="1:20" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="215" t="s">
+      <c r="A16" s="227" t="s">
         <v>71</v>
       </c>
-      <c r="B16" s="216"/>
-      <c r="C16" s="201" t="s">
+      <c r="B16" s="228"/>
+      <c r="C16" s="213" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="201"/>
-      <c r="E16" s="201"/>
-      <c r="F16" s="201" t="s">
+      <c r="D16" s="213"/>
+      <c r="E16" s="213"/>
+      <c r="F16" s="213" t="s">
         <v>70</v>
       </c>
-      <c r="G16" s="201"/>
-      <c r="H16" s="201"/>
-      <c r="I16" s="222" t="s">
+      <c r="G16" s="213"/>
+      <c r="H16" s="213"/>
+      <c r="I16" s="234" t="s">
         <v>3</v>
       </c>
-      <c r="J16" s="222"/>
-      <c r="K16" s="201" t="s">
+      <c r="J16" s="234"/>
+      <c r="K16" s="213" t="s">
         <v>5</v>
       </c>
-      <c r="L16" s="202"/>
+      <c r="L16" s="214"/>
     </row>
     <row r="17" spans="1:20" ht="22.9" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="203" t="s">
+      <c r="A17" s="215" t="s">
         <v>68</v>
       </c>
-      <c r="B17" s="204"/>
-      <c r="C17" s="217"/>
-      <c r="D17" s="217"/>
-      <c r="E17" s="217"/>
-      <c r="F17" s="220"/>
-      <c r="G17" s="204"/>
-      <c r="H17" s="221"/>
-      <c r="I17" s="223"/>
-      <c r="J17" s="223"/>
-      <c r="K17" s="218"/>
-      <c r="L17" s="219"/>
+      <c r="B17" s="216"/>
+      <c r="C17" s="229"/>
+      <c r="D17" s="229"/>
+      <c r="E17" s="229"/>
+      <c r="F17" s="232"/>
+      <c r="G17" s="216"/>
+      <c r="H17" s="233"/>
+      <c r="I17" s="235"/>
+      <c r="J17" s="235"/>
+      <c r="K17" s="230"/>
+      <c r="L17" s="231"/>
     </row>
     <row r="18" spans="1:20" ht="23.45" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="203" t="s">
+      <c r="A18" s="215" t="s">
         <v>69</v>
       </c>
-      <c r="B18" s="204"/>
-      <c r="C18" s="217"/>
-      <c r="D18" s="217"/>
-      <c r="E18" s="217"/>
-      <c r="F18" s="220"/>
-      <c r="G18" s="204"/>
-      <c r="H18" s="221"/>
-      <c r="I18" s="224"/>
-      <c r="J18" s="225"/>
+      <c r="B18" s="216"/>
+      <c r="C18" s="229"/>
+      <c r="D18" s="229"/>
+      <c r="E18" s="229"/>
+      <c r="F18" s="232"/>
+      <c r="G18" s="216"/>
+      <c r="H18" s="233"/>
+      <c r="I18" s="236"/>
+      <c r="J18" s="237"/>
       <c r="K18" s="45"/>
       <c r="L18" s="60"/>
       <c r="T18" s="4"/>
@@ -4173,278 +4370,278 @@
       <c r="B19" s="107" t="s">
         <v>2</v>
       </c>
-      <c r="C19" s="143" t="s">
+      <c r="C19" s="155" t="s">
         <v>3</v>
       </c>
-      <c r="D19" s="143"/>
-      <c r="E19" s="184"/>
-      <c r="F19" s="182" t="s">
+      <c r="D19" s="155"/>
+      <c r="E19" s="196"/>
+      <c r="F19" s="194" t="s">
         <v>4</v>
       </c>
-      <c r="G19" s="183"/>
-      <c r="H19" s="183"/>
-      <c r="I19" s="183"/>
-      <c r="J19" s="183"/>
-      <c r="K19" s="184" t="s">
+      <c r="G19" s="195"/>
+      <c r="H19" s="195"/>
+      <c r="I19" s="195"/>
+      <c r="J19" s="195"/>
+      <c r="K19" s="196" t="s">
         <v>5</v>
       </c>
-      <c r="L19" s="185"/>
+      <c r="L19" s="197"/>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="99">
         <v>0</v>
       </c>
       <c r="B20" s="100"/>
-      <c r="C20" s="177" t="s">
-        <v>152</v>
-      </c>
-      <c r="D20" s="177"/>
-      <c r="E20" s="177"/>
-      <c r="F20" s="178" t="s">
-        <v>156</v>
-      </c>
-      <c r="G20" s="179"/>
-      <c r="H20" s="179"/>
-      <c r="I20" s="179"/>
-      <c r="J20" s="179"/>
-      <c r="K20" s="180">
+      <c r="C20" s="189" t="s">
+        <v>151</v>
+      </c>
+      <c r="D20" s="189"/>
+      <c r="E20" s="189"/>
+      <c r="F20" s="190" t="s">
+        <v>155</v>
+      </c>
+      <c r="G20" s="191"/>
+      <c r="H20" s="191"/>
+      <c r="I20" s="191"/>
+      <c r="J20" s="191"/>
+      <c r="K20" s="192">
         <v>46187</v>
       </c>
-      <c r="L20" s="181"/>
+      <c r="L20" s="193"/>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="61">
         <v>2</v>
       </c>
       <c r="B21" s="12"/>
-      <c r="C21" s="172"/>
-      <c r="D21" s="172"/>
-      <c r="E21" s="172"/>
-      <c r="F21" s="173"/>
-      <c r="G21" s="174"/>
-      <c r="H21" s="174"/>
-      <c r="I21" s="174"/>
-      <c r="J21" s="174"/>
-      <c r="K21" s="175"/>
-      <c r="L21" s="176"/>
+      <c r="C21" s="184"/>
+      <c r="D21" s="184"/>
+      <c r="E21" s="184"/>
+      <c r="F21" s="185"/>
+      <c r="G21" s="186"/>
+      <c r="H21" s="186"/>
+      <c r="I21" s="186"/>
+      <c r="J21" s="186"/>
+      <c r="K21" s="187"/>
+      <c r="L21" s="188"/>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="62">
         <v>3</v>
       </c>
       <c r="B22" s="54"/>
-      <c r="C22" s="159"/>
-      <c r="D22" s="159"/>
-      <c r="E22" s="159"/>
-      <c r="F22" s="160"/>
-      <c r="G22" s="161"/>
-      <c r="H22" s="161"/>
-      <c r="I22" s="161"/>
-      <c r="J22" s="161"/>
-      <c r="K22" s="170"/>
-      <c r="L22" s="171"/>
+      <c r="C22" s="171"/>
+      <c r="D22" s="171"/>
+      <c r="E22" s="171"/>
+      <c r="F22" s="172"/>
+      <c r="G22" s="173"/>
+      <c r="H22" s="173"/>
+      <c r="I22" s="173"/>
+      <c r="J22" s="173"/>
+      <c r="K22" s="182"/>
+      <c r="L22" s="183"/>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="62">
         <v>4</v>
       </c>
       <c r="B23" s="54"/>
-      <c r="C23" s="159"/>
-      <c r="D23" s="159"/>
-      <c r="E23" s="159"/>
-      <c r="F23" s="160"/>
-      <c r="G23" s="161"/>
-      <c r="H23" s="161"/>
-      <c r="I23" s="161"/>
-      <c r="J23" s="161"/>
-      <c r="K23" s="170"/>
-      <c r="L23" s="171"/>
+      <c r="C23" s="171"/>
+      <c r="D23" s="171"/>
+      <c r="E23" s="171"/>
+      <c r="F23" s="172"/>
+      <c r="G23" s="173"/>
+      <c r="H23" s="173"/>
+      <c r="I23" s="173"/>
+      <c r="J23" s="173"/>
+      <c r="K23" s="182"/>
+      <c r="L23" s="183"/>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="62">
         <v>5</v>
       </c>
       <c r="B24" s="54"/>
-      <c r="C24" s="159"/>
-      <c r="D24" s="159"/>
-      <c r="E24" s="159"/>
-      <c r="F24" s="160"/>
-      <c r="G24" s="161"/>
-      <c r="H24" s="161"/>
-      <c r="I24" s="161"/>
-      <c r="J24" s="161"/>
-      <c r="K24" s="170"/>
-      <c r="L24" s="171"/>
+      <c r="C24" s="171"/>
+      <c r="D24" s="171"/>
+      <c r="E24" s="171"/>
+      <c r="F24" s="172"/>
+      <c r="G24" s="173"/>
+      <c r="H24" s="173"/>
+      <c r="I24" s="173"/>
+      <c r="J24" s="173"/>
+      <c r="K24" s="182"/>
+      <c r="L24" s="183"/>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="62"/>
       <c r="B25" s="54"/>
-      <c r="C25" s="159"/>
-      <c r="D25" s="159"/>
-      <c r="E25" s="159"/>
-      <c r="F25" s="168"/>
-      <c r="G25" s="169"/>
-      <c r="H25" s="169"/>
-      <c r="I25" s="169"/>
-      <c r="J25" s="169"/>
-      <c r="K25" s="170"/>
-      <c r="L25" s="171"/>
+      <c r="C25" s="171"/>
+      <c r="D25" s="171"/>
+      <c r="E25" s="171"/>
+      <c r="F25" s="180"/>
+      <c r="G25" s="181"/>
+      <c r="H25" s="181"/>
+      <c r="I25" s="181"/>
+      <c r="J25" s="181"/>
+      <c r="K25" s="182"/>
+      <c r="L25" s="183"/>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="62"/>
       <c r="B26" s="54"/>
-      <c r="C26" s="159"/>
-      <c r="D26" s="159"/>
-      <c r="E26" s="159"/>
-      <c r="F26" s="160"/>
-      <c r="G26" s="161"/>
-      <c r="H26" s="161"/>
-      <c r="I26" s="161"/>
-      <c r="J26" s="161"/>
-      <c r="K26" s="170"/>
-      <c r="L26" s="171"/>
+      <c r="C26" s="171"/>
+      <c r="D26" s="171"/>
+      <c r="E26" s="171"/>
+      <c r="F26" s="172"/>
+      <c r="G26" s="173"/>
+      <c r="H26" s="173"/>
+      <c r="I26" s="173"/>
+      <c r="J26" s="173"/>
+      <c r="K26" s="182"/>
+      <c r="L26" s="183"/>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="62"/>
       <c r="B27" s="54"/>
-      <c r="C27" s="159"/>
-      <c r="D27" s="159"/>
-      <c r="E27" s="159"/>
-      <c r="F27" s="168"/>
-      <c r="G27" s="169"/>
-      <c r="H27" s="169"/>
-      <c r="I27" s="169"/>
-      <c r="J27" s="169"/>
-      <c r="K27" s="170"/>
-      <c r="L27" s="171"/>
+      <c r="C27" s="171"/>
+      <c r="D27" s="171"/>
+      <c r="E27" s="171"/>
+      <c r="F27" s="180"/>
+      <c r="G27" s="181"/>
+      <c r="H27" s="181"/>
+      <c r="I27" s="181"/>
+      <c r="J27" s="181"/>
+      <c r="K27" s="182"/>
+      <c r="L27" s="183"/>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="62"/>
       <c r="B28" s="54"/>
-      <c r="C28" s="159"/>
-      <c r="D28" s="159"/>
-      <c r="E28" s="159"/>
-      <c r="F28" s="160"/>
-      <c r="G28" s="169"/>
-      <c r="H28" s="169"/>
-      <c r="I28" s="169"/>
-      <c r="J28" s="169"/>
-      <c r="K28" s="170"/>
-      <c r="L28" s="171"/>
+      <c r="C28" s="171"/>
+      <c r="D28" s="171"/>
+      <c r="E28" s="171"/>
+      <c r="F28" s="172"/>
+      <c r="G28" s="181"/>
+      <c r="H28" s="181"/>
+      <c r="I28" s="181"/>
+      <c r="J28" s="181"/>
+      <c r="K28" s="182"/>
+      <c r="L28" s="183"/>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="62"/>
       <c r="B29" s="54"/>
-      <c r="C29" s="159"/>
-      <c r="D29" s="159"/>
-      <c r="E29" s="159"/>
-      <c r="F29" s="160"/>
-      <c r="G29" s="161"/>
-      <c r="H29" s="161"/>
-      <c r="I29" s="161"/>
-      <c r="J29" s="161"/>
-      <c r="K29" s="162"/>
-      <c r="L29" s="163"/>
+      <c r="C29" s="171"/>
+      <c r="D29" s="171"/>
+      <c r="E29" s="171"/>
+      <c r="F29" s="172"/>
+      <c r="G29" s="173"/>
+      <c r="H29" s="173"/>
+      <c r="I29" s="173"/>
+      <c r="J29" s="173"/>
+      <c r="K29" s="174"/>
+      <c r="L29" s="175"/>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="63"/>
       <c r="B30" s="53"/>
-      <c r="C30" s="164"/>
-      <c r="D30" s="164"/>
-      <c r="E30" s="164"/>
-      <c r="F30" s="165"/>
-      <c r="G30" s="166"/>
-      <c r="H30" s="166"/>
-      <c r="I30" s="166"/>
-      <c r="J30" s="166"/>
-      <c r="K30" s="164"/>
-      <c r="L30" s="167"/>
+      <c r="C30" s="176"/>
+      <c r="D30" s="176"/>
+      <c r="E30" s="176"/>
+      <c r="F30" s="177"/>
+      <c r="G30" s="178"/>
+      <c r="H30" s="178"/>
+      <c r="I30" s="178"/>
+      <c r="J30" s="178"/>
+      <c r="K30" s="176"/>
+      <c r="L30" s="179"/>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="58"/>
       <c r="B31" s="10"/>
-      <c r="C31" s="138"/>
-      <c r="D31" s="138"/>
-      <c r="E31" s="138"/>
-      <c r="F31" s="147"/>
-      <c r="G31" s="148"/>
-      <c r="H31" s="148"/>
-      <c r="I31" s="148"/>
-      <c r="J31" s="148"/>
-      <c r="K31" s="138"/>
-      <c r="L31" s="135"/>
+      <c r="C31" s="150"/>
+      <c r="D31" s="150"/>
+      <c r="E31" s="150"/>
+      <c r="F31" s="159"/>
+      <c r="G31" s="160"/>
+      <c r="H31" s="160"/>
+      <c r="I31" s="160"/>
+      <c r="J31" s="160"/>
+      <c r="K31" s="150"/>
+      <c r="L31" s="147"/>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="58"/>
       <c r="B32" s="10"/>
-      <c r="C32" s="138"/>
-      <c r="D32" s="138"/>
-      <c r="E32" s="138"/>
-      <c r="F32" s="147"/>
-      <c r="G32" s="148"/>
-      <c r="H32" s="148"/>
-      <c r="I32" s="148"/>
-      <c r="J32" s="148"/>
-      <c r="K32" s="138"/>
-      <c r="L32" s="135"/>
+      <c r="C32" s="150"/>
+      <c r="D32" s="150"/>
+      <c r="E32" s="150"/>
+      <c r="F32" s="159"/>
+      <c r="G32" s="160"/>
+      <c r="H32" s="160"/>
+      <c r="I32" s="160"/>
+      <c r="J32" s="160"/>
+      <c r="K32" s="150"/>
+      <c r="L32" s="147"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="58"/>
       <c r="B33" s="10"/>
-      <c r="C33" s="138"/>
-      <c r="D33" s="138"/>
-      <c r="E33" s="138"/>
-      <c r="F33" s="147"/>
-      <c r="G33" s="148"/>
-      <c r="H33" s="148"/>
-      <c r="I33" s="148"/>
-      <c r="J33" s="148"/>
-      <c r="K33" s="138"/>
-      <c r="L33" s="135"/>
+      <c r="C33" s="150"/>
+      <c r="D33" s="150"/>
+      <c r="E33" s="150"/>
+      <c r="F33" s="159"/>
+      <c r="G33" s="160"/>
+      <c r="H33" s="160"/>
+      <c r="I33" s="160"/>
+      <c r="J33" s="160"/>
+      <c r="K33" s="150"/>
+      <c r="L33" s="147"/>
     </row>
     <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="59"/>
       <c r="B34" s="19"/>
-      <c r="C34" s="136"/>
-      <c r="D34" s="136"/>
-      <c r="E34" s="136"/>
-      <c r="F34" s="157"/>
-      <c r="G34" s="158"/>
-      <c r="H34" s="158"/>
-      <c r="I34" s="158"/>
-      <c r="J34" s="158"/>
-      <c r="K34" s="136"/>
-      <c r="L34" s="137"/>
+      <c r="C34" s="148"/>
+      <c r="D34" s="148"/>
+      <c r="E34" s="148"/>
+      <c r="F34" s="169"/>
+      <c r="G34" s="170"/>
+      <c r="H34" s="170"/>
+      <c r="I34" s="170"/>
+      <c r="J34" s="170"/>
+      <c r="K34" s="148"/>
+      <c r="L34" s="149"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="149" t="s">
+      <c r="A35" s="161" t="s">
         <v>14</v>
       </c>
-      <c r="B35" s="150"/>
-      <c r="C35" s="151"/>
-      <c r="D35" s="151"/>
-      <c r="E35" s="151"/>
-      <c r="F35" s="151"/>
-      <c r="G35" s="151"/>
-      <c r="H35" s="151"/>
-      <c r="I35" s="151"/>
-      <c r="J35" s="151"/>
-      <c r="K35" s="151"/>
-      <c r="L35" s="152"/>
+      <c r="B35" s="162"/>
+      <c r="C35" s="163"/>
+      <c r="D35" s="163"/>
+      <c r="E35" s="163"/>
+      <c r="F35" s="163"/>
+      <c r="G35" s="163"/>
+      <c r="H35" s="163"/>
+      <c r="I35" s="163"/>
+      <c r="J35" s="163"/>
+      <c r="K35" s="163"/>
+      <c r="L35" s="164"/>
     </row>
     <row r="36" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="153"/>
-      <c r="B36" s="154"/>
-      <c r="C36" s="154"/>
-      <c r="D36" s="154"/>
-      <c r="E36" s="154"/>
-      <c r="F36" s="154"/>
-      <c r="G36" s="154"/>
-      <c r="H36" s="154"/>
-      <c r="I36" s="154"/>
-      <c r="J36" s="154"/>
-      <c r="K36" s="154"/>
-      <c r="L36" s="155"/>
+      <c r="A36" s="165"/>
+      <c r="B36" s="166"/>
+      <c r="C36" s="166"/>
+      <c r="D36" s="166"/>
+      <c r="E36" s="166"/>
+      <c r="F36" s="166"/>
+      <c r="G36" s="166"/>
+      <c r="H36" s="166"/>
+      <c r="I36" s="166"/>
+      <c r="J36" s="166"/>
+      <c r="K36" s="166"/>
+      <c r="L36" s="167"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="106" t="s">
@@ -4462,19 +4659,19 @@
       <c r="E37" s="107" t="s">
         <v>78</v>
       </c>
-      <c r="F37" s="144" t="s">
+      <c r="F37" s="156" t="s">
         <v>44</v>
       </c>
-      <c r="G37" s="145"/>
-      <c r="H37" s="146"/>
-      <c r="I37" s="143" t="s">
+      <c r="G37" s="157"/>
+      <c r="H37" s="158"/>
+      <c r="I37" s="155" t="s">
         <v>19</v>
       </c>
-      <c r="J37" s="143"/>
-      <c r="K37" s="143" t="s">
+      <c r="J37" s="155"/>
+      <c r="K37" s="155" t="s">
         <v>5</v>
       </c>
-      <c r="L37" s="156"/>
+      <c r="L37" s="168"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="58">
@@ -4484,13 +4681,13 @@
       <c r="C38" s="10"/>
       <c r="D38" s="10"/>
       <c r="E38" s="10"/>
-      <c r="F38" s="138"/>
-      <c r="G38" s="138"/>
-      <c r="H38" s="138"/>
-      <c r="I38" s="139"/>
-      <c r="J38" s="140"/>
-      <c r="K38" s="134"/>
-      <c r="L38" s="135"/>
+      <c r="F38" s="150"/>
+      <c r="G38" s="150"/>
+      <c r="H38" s="150"/>
+      <c r="I38" s="151"/>
+      <c r="J38" s="152"/>
+      <c r="K38" s="146"/>
+      <c r="L38" s="147"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="58">
@@ -4500,13 +4697,13 @@
       <c r="C39" s="10"/>
       <c r="D39" s="10"/>
       <c r="E39" s="10"/>
-      <c r="F39" s="138"/>
-      <c r="G39" s="138"/>
-      <c r="H39" s="138"/>
-      <c r="I39" s="139"/>
-      <c r="J39" s="140"/>
-      <c r="K39" s="134"/>
-      <c r="L39" s="135"/>
+      <c r="F39" s="150"/>
+      <c r="G39" s="150"/>
+      <c r="H39" s="150"/>
+      <c r="I39" s="151"/>
+      <c r="J39" s="152"/>
+      <c r="K39" s="146"/>
+      <c r="L39" s="147"/>
     </row>
     <row r="40" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="59"/>
@@ -4514,13 +4711,13 @@
       <c r="C40" s="14"/>
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
-      <c r="F40" s="136"/>
-      <c r="G40" s="136"/>
-      <c r="H40" s="136"/>
-      <c r="I40" s="141"/>
-      <c r="J40" s="142"/>
-      <c r="K40" s="136"/>
-      <c r="L40" s="137"/>
+      <c r="F40" s="148"/>
+      <c r="G40" s="148"/>
+      <c r="H40" s="148"/>
+      <c r="I40" s="153"/>
+      <c r="J40" s="154"/>
+      <c r="K40" s="148"/>
+      <c r="L40" s="149"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B42" s="48"/>
@@ -4632,48 +4829,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="232" t="s">
-        <v>160</v>
-      </c>
-      <c r="B1" s="233"/>
-      <c r="C1" s="238" t="s">
+      <c r="A1" s="244" t="s">
+        <v>158</v>
+      </c>
+      <c r="B1" s="245"/>
+      <c r="C1" s="250" t="s">
         <v>93</v>
       </c>
-      <c r="D1" s="239"/>
-      <c r="E1" s="239"/>
-      <c r="F1" s="239"/>
-      <c r="G1" s="239"/>
-      <c r="H1" s="239"/>
-      <c r="I1" s="239"/>
+      <c r="D1" s="251"/>
+      <c r="E1" s="251"/>
+      <c r="F1" s="251"/>
+      <c r="G1" s="251"/>
+      <c r="H1" s="251"/>
+      <c r="I1" s="251"/>
     </row>
     <row r="2" spans="1:32" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="234"/>
-      <c r="B2" s="235"/>
-      <c r="C2" s="111" t="s">
+      <c r="A2" s="246"/>
+      <c r="B2" s="247"/>
+      <c r="C2" s="123" t="s">
         <v>117</v>
       </c>
-      <c r="D2" s="111" t="s">
-        <v>157</v>
-      </c>
-      <c r="E2" s="111"/>
-      <c r="F2" s="111"/>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="111"/>
+      <c r="D2" s="123" t="s">
+        <v>203</v>
+      </c>
+      <c r="E2" s="123" t="s">
+        <v>201</v>
+      </c>
+      <c r="F2" s="123" t="s">
+        <v>202</v>
+      </c>
+      <c r="G2" s="123"/>
+      <c r="H2" s="123"/>
+      <c r="I2" s="123"/>
     </row>
     <row r="3" spans="1:32" ht="147.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="236"/>
-      <c r="B3" s="237"/>
-      <c r="C3" s="111"/>
-      <c r="D3" s="111"/>
-      <c r="E3" s="111"/>
-      <c r="F3" s="111"/>
-      <c r="G3" s="111"/>
-      <c r="H3" s="111"/>
-      <c r="I3" s="111"/>
+      <c r="A3" s="248"/>
+      <c r="B3" s="249"/>
+      <c r="C3" s="123"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="123"/>
+      <c r="F3" s="123"/>
+      <c r="G3" s="123"/>
+      <c r="H3" s="123"/>
+      <c r="I3" s="123"/>
     </row>
     <row r="4" spans="1:32" ht="55.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="226" t="s">
+      <c r="A4" s="238" t="s">
         <v>92</v>
       </c>
       <c r="B4" s="105" t="s">
@@ -4693,7 +4894,7 @@
       </c>
     </row>
     <row r="5" spans="1:32" ht="55.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="227"/>
+      <c r="A5" s="239"/>
       <c r="B5" s="105" t="s">
         <v>120</v>
       </c>
@@ -4710,7 +4911,7 @@
       <c r="I5" s="85"/>
     </row>
     <row r="6" spans="1:32" ht="55.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="227"/>
+      <c r="A6" s="239"/>
       <c r="B6" s="105"/>
       <c r="C6" s="86"/>
       <c r="D6" s="83"/>
@@ -4721,7 +4922,7 @@
       <c r="I6" s="85"/>
     </row>
     <row r="7" spans="1:32" ht="55.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="227"/>
+      <c r="A7" s="239"/>
       <c r="B7" s="105"/>
       <c r="C7" s="86"/>
       <c r="D7" s="83"/>
@@ -4732,7 +4933,7 @@
       <c r="I7" s="85"/>
     </row>
     <row r="8" spans="1:32" ht="55.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="227"/>
+      <c r="A8" s="239"/>
       <c r="B8" s="105"/>
       <c r="C8" s="86"/>
       <c r="D8" s="83"/>
@@ -4743,7 +4944,7 @@
       <c r="I8" s="87"/>
     </row>
     <row r="9" spans="1:32" ht="55.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="227"/>
+      <c r="A9" s="239"/>
       <c r="B9" s="105"/>
       <c r="C9" s="79"/>
       <c r="D9" s="88"/>
@@ -4754,7 +4955,7 @@
       <c r="I9" s="91"/>
     </row>
     <row r="10" spans="1:32" ht="55.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="227"/>
+      <c r="A10" s="239"/>
       <c r="B10" s="105"/>
       <c r="C10" s="89"/>
       <c r="D10" s="89"/>
@@ -4765,7 +4966,7 @@
       <c r="I10" s="91"/>
     </row>
     <row r="11" spans="1:32" ht="55.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="227"/>
+      <c r="A11" s="239"/>
       <c r="B11" s="105"/>
       <c r="C11" s="89"/>
       <c r="D11" s="89"/>
@@ -4776,7 +4977,7 @@
       <c r="I11" s="91"/>
     </row>
     <row r="12" spans="1:32" ht="55.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="228"/>
+      <c r="A12" s="240"/>
       <c r="B12" s="105"/>
       <c r="C12" s="93"/>
       <c r="D12" s="93"/>
@@ -4788,17 +4989,17 @@
     </row>
     <row r="14" spans="1:32" ht="32.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="1:32" ht="32.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="229" t="s">
+      <c r="A15" s="241" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="230"/>
-      <c r="C15" s="230"/>
-      <c r="D15" s="230"/>
-      <c r="E15" s="230"/>
-      <c r="F15" s="230"/>
-      <c r="G15" s="230"/>
-      <c r="H15" s="230"/>
-      <c r="I15" s="231"/>
+      <c r="B15" s="242"/>
+      <c r="C15" s="242"/>
+      <c r="D15" s="242"/>
+      <c r="E15" s="242"/>
+      <c r="F15" s="242"/>
+      <c r="G15" s="242"/>
+      <c r="H15" s="242"/>
+      <c r="I15" s="243"/>
       <c r="J15" s="96"/>
     </row>
     <row r="16" spans="1:32" ht="32.1" customHeight="1" x14ac:dyDescent="0.5">
@@ -5153,123 +5354,126 @@
     <col min="17" max="17" width="10.140625" customWidth="1" collapsed="1"/>
     <col min="18" max="18" width="14.28515625" customWidth="1"/>
     <col min="19" max="19" width="15" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="11.7109375" customWidth="1"/>
+    <col min="20" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="136" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="125"/>
-      <c r="E1" s="119" t="s">
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="109" t="s">
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="132"/>
+      <c r="I1" s="132"/>
+      <c r="J1" s="132"/>
+      <c r="K1" s="132"/>
+      <c r="L1" s="132"/>
+      <c r="M1" s="132"/>
+      <c r="N1" s="132"/>
+      <c r="O1" s="132"/>
+      <c r="P1" s="132"/>
+      <c r="Q1" s="132"/>
+      <c r="R1" s="133"/>
+      <c r="S1" s="121" t="s">
         <v>25</v>
       </c>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
-      <c r="V1" s="110"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
     </row>
     <row r="2" spans="1:22" s="2" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="115" t="s">
+      <c r="A2" s="127" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="115"/>
-      <c r="C2" s="126" t="s">
+      <c r="B2" s="127"/>
+      <c r="C2" s="138" t="s">
         <v>116</v>
       </c>
-      <c r="D2" s="127"/>
-      <c r="E2" s="132" t="s">
+      <c r="D2" s="139"/>
+      <c r="E2" s="144" t="s">
         <v>80</v>
       </c>
-      <c r="F2" s="111" t="s">
+      <c r="F2" s="123" t="s">
         <v>87</v>
       </c>
-      <c r="G2" s="111" t="s">
+      <c r="G2" s="123" t="s">
         <v>81</v>
       </c>
-      <c r="H2" s="111" t="s">
+      <c r="H2" s="123" t="s">
         <v>82</v>
       </c>
-      <c r="I2" s="111" t="s">
+      <c r="I2" s="123" t="s">
         <v>83</v>
       </c>
-      <c r="J2" s="111" t="s">
+      <c r="J2" s="123" t="s">
         <v>84</v>
       </c>
-      <c r="K2" s="111" t="s">
+      <c r="K2" s="123" t="s">
         <v>85</v>
       </c>
-      <c r="L2" s="111" t="s">
+      <c r="L2" s="123" t="s">
         <v>86</v>
       </c>
-      <c r="M2" s="117" t="s">
+      <c r="M2" s="129" t="s">
         <v>111</v>
       </c>
-      <c r="N2" s="117" t="s">
+      <c r="N2" s="129" t="s">
         <v>76</v>
       </c>
-      <c r="O2" s="130" t="s">
+      <c r="O2" s="142" t="s">
         <v>34</v>
       </c>
-      <c r="P2" s="130" t="s">
+      <c r="P2" s="142" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="130" t="s">
+      <c r="Q2" s="142" t="s">
         <v>15</v>
       </c>
-      <c r="R2" s="122" t="s">
+      <c r="R2" s="134" t="s">
         <v>17</v>
       </c>
-      <c r="S2" s="112" t="s">
+      <c r="S2" s="124" t="s">
         <v>6</v>
       </c>
-      <c r="T2" s="112" t="s">
-        <v>153</v>
-      </c>
-      <c r="U2" s="112"/>
-      <c r="V2" s="112"/>
+      <c r="T2" s="124" t="s">
+        <v>152</v>
+      </c>
+      <c r="U2" s="124" t="s">
+        <v>199</v>
+      </c>
+      <c r="V2" s="124" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="3" spans="1:22" s="2" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="116"/>
-      <c r="B3" s="116"/>
-      <c r="C3" s="128"/>
-      <c r="D3" s="129"/>
-      <c r="E3" s="132"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="111"/>
-      <c r="H3" s="111"/>
-      <c r="I3" s="111"/>
-      <c r="J3" s="111"/>
-      <c r="K3" s="111"/>
-      <c r="L3" s="111"/>
-      <c r="M3" s="118"/>
-      <c r="N3" s="118"/>
-      <c r="O3" s="131"/>
-      <c r="P3" s="131"/>
-      <c r="Q3" s="131"/>
-      <c r="R3" s="123"/>
-      <c r="S3" s="113"/>
-      <c r="T3" s="113"/>
-      <c r="U3" s="113"/>
-      <c r="V3" s="113"/>
+      <c r="A3" s="128"/>
+      <c r="B3" s="128"/>
+      <c r="C3" s="140"/>
+      <c r="D3" s="141"/>
+      <c r="E3" s="144"/>
+      <c r="F3" s="145"/>
+      <c r="G3" s="123"/>
+      <c r="H3" s="123"/>
+      <c r="I3" s="123"/>
+      <c r="J3" s="123"/>
+      <c r="K3" s="123"/>
+      <c r="L3" s="123"/>
+      <c r="M3" s="130"/>
+      <c r="N3" s="130"/>
+      <c r="O3" s="143"/>
+      <c r="P3" s="143"/>
+      <c r="Q3" s="143"/>
+      <c r="R3" s="135"/>
+      <c r="S3" s="125"/>
+      <c r="T3" s="125"/>
+      <c r="U3" s="125"/>
+      <c r="V3" s="125"/>
     </row>
     <row r="4" spans="1:22" s="2" customFormat="1" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
@@ -5284,24 +5488,24 @@
       <c r="D4" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="132"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="111"/>
-      <c r="L4" s="111"/>
-      <c r="M4" s="118"/>
-      <c r="N4" s="118"/>
-      <c r="O4" s="131"/>
-      <c r="P4" s="131"/>
-      <c r="Q4" s="131"/>
-      <c r="R4" s="123"/>
-      <c r="S4" s="114"/>
-      <c r="T4" s="114"/>
-      <c r="U4" s="114"/>
-      <c r="V4" s="114"/>
+      <c r="E4" s="144"/>
+      <c r="F4" s="145"/>
+      <c r="G4" s="123"/>
+      <c r="H4" s="123"/>
+      <c r="I4" s="123"/>
+      <c r="J4" s="123"/>
+      <c r="K4" s="123"/>
+      <c r="L4" s="123"/>
+      <c r="M4" s="130"/>
+      <c r="N4" s="130"/>
+      <c r="O4" s="143"/>
+      <c r="P4" s="143"/>
+      <c r="Q4" s="143"/>
+      <c r="R4" s="135"/>
+      <c r="S4" s="126"/>
+      <c r="T4" s="126"/>
+      <c r="U4" s="126"/>
+      <c r="V4" s="126"/>
     </row>
     <row r="5" spans="1:22" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
@@ -5312,7 +5516,7 @@
         <v>126</v>
       </c>
       <c r="F5" s="101" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>129</v>
@@ -5424,10 +5628,10 @@
         <v>127</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>130</v>
@@ -5439,10 +5643,10 @@
         <v>122</v>
       </c>
       <c r="K7" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="L7" s="7" t="s">
         <v>141</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>142</v>
       </c>
       <c r="M7" s="65" t="str">
         <f>CONCATENATE(J7,K7,L7)</f>
@@ -5479,10 +5683,10 @@
         <v>127</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>134</v>
@@ -5494,17 +5698,17 @@
         <v>122</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M8" s="65" t="str">
         <f t="shared" ref="M8" si="0">CONCATENATE(J8,K8,L8)</f>
         <v>=S1+SG2-B1</v>
       </c>
       <c r="N8" s="49" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O8" s="8" t="s">
         <v>37</v>
@@ -5534,7 +5738,7 @@
         <v>126</v>
       </c>
       <c r="F9" s="101" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>129</v>
@@ -5549,10 +5753,10 @@
         <v>122</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="M9" s="65" t="str">
         <f>CONCATENATE(J9,K9,L9)</f>
@@ -5598,7 +5802,7 @@
         <v>134</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>137</v>
+        <v>168</v>
       </c>
       <c r="J10" s="7" t="s">
         <v>122</v>
@@ -5629,10 +5833,10 @@
         <v>6</v>
       </c>
       <c r="S10" s="98" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="T10" s="98" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="U10" s="74"/>
       <c r="V10" s="10"/>
@@ -5642,25 +5846,53 @@
       <c r="B11" s="51"/>
       <c r="C11" s="6"/>
       <c r="D11" s="32"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
+      <c r="E11" s="97" t="s">
+        <v>126</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="L11" s="109" t="s">
+        <v>170</v>
+      </c>
       <c r="M11" s="65" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="N11" s="49"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="20"/>
-      <c r="R11" s="73"/>
+        <v>=S1+MS1.CC1-S67008</v>
+      </c>
+      <c r="N11" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="O11" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="P11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q11" s="20">
+        <v>0</v>
+      </c>
+      <c r="R11" s="73" t="s">
+        <v>6</v>
+      </c>
       <c r="S11" s="74"/>
-      <c r="T11" s="74"/>
+      <c r="T11" s="74" t="s">
+        <v>150</v>
+      </c>
       <c r="U11" s="74"/>
       <c r="V11" s="10"/>
     </row>
@@ -5669,25 +5901,45 @@
       <c r="B12" s="51"/>
       <c r="C12" s="6"/>
       <c r="D12" s="32"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
+      <c r="E12" s="97" t="s">
+        <v>126</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>174</v>
+      </c>
       <c r="M12" s="65" t="str">
-        <f t="shared" ref="M12:M21" si="2">CONCATENATE(J12,K12,L12)</f>
-        <v/>
+        <f t="shared" ref="M12" si="2">CONCATENATE(J12,K12,L12)</f>
+        <v>=S1+MS1.CC1-X40001</v>
       </c>
       <c r="N12" s="49"/>
       <c r="O12" s="8"/>
       <c r="P12" s="9"/>
       <c r="Q12" s="20"/>
       <c r="R12" s="73"/>
-      <c r="S12" s="74"/>
-      <c r="T12" s="74"/>
+      <c r="S12" s="74" t="s">
+        <v>115</v>
+      </c>
+      <c r="T12" s="74" t="s">
+        <v>115</v>
+      </c>
       <c r="U12" s="74"/>
       <c r="V12" s="10"/>
     </row>
@@ -5705,7 +5957,7 @@
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
       <c r="M13" s="65" t="str">
-        <f t="shared" ref="M13:M19" si="3">CONCATENATE(J13,K13,L13)</f>
+        <f t="shared" ref="M13" si="3">CONCATENATE(J13,K13,L13)</f>
         <v/>
       </c>
       <c r="N13" s="49"/>
@@ -5723,26 +5975,58 @@
       <c r="B14" s="51"/>
       <c r="C14" s="6"/>
       <c r="D14" s="32"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="N14" s="49"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="9"/>
-      <c r="Q14" s="20"/>
-      <c r="R14" s="73"/>
-      <c r="S14" s="74"/>
-      <c r="T14" s="74"/>
-      <c r="U14" s="74"/>
+      <c r="E14" s="113" t="s">
+        <v>184</v>
+      </c>
+      <c r="F14" s="101" t="s">
+        <v>185</v>
+      </c>
+      <c r="G14" s="112" t="s">
+        <v>129</v>
+      </c>
+      <c r="H14" s="112" t="s">
+        <v>130</v>
+      </c>
+      <c r="I14" s="112" t="s">
+        <v>121</v>
+      </c>
+      <c r="J14" s="112" t="s">
+        <v>193</v>
+      </c>
+      <c r="K14" s="112" t="s">
+        <v>196</v>
+      </c>
+      <c r="L14" s="112" t="s">
+        <v>128</v>
+      </c>
+      <c r="M14" s="114" t="str">
+        <f>CONCATENATE(J14,K14,L14)</f>
+        <v>=S2+MS2.CC1-S67001</v>
+      </c>
+      <c r="N14" s="115" t="s">
+        <v>22</v>
+      </c>
+      <c r="O14" s="116" t="s">
+        <v>37</v>
+      </c>
+      <c r="P14" s="117" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q14" s="118">
+        <v>0</v>
+      </c>
+      <c r="R14" s="119" t="s">
+        <v>6</v>
+      </c>
+      <c r="S14" s="74" t="s">
+        <v>198</v>
+      </c>
+      <c r="T14" s="74" t="s">
+        <v>198</v>
+      </c>
+      <c r="U14" s="74" t="s">
+        <v>198</v>
+      </c>
       <c r="V14" s="10"/>
     </row>
     <row r="15" spans="1:22" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -5750,26 +6034,54 @@
       <c r="B15" s="51"/>
       <c r="C15" s="6"/>
       <c r="D15" s="32"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="N15" s="49"/>
-      <c r="O15" s="8"/>
-      <c r="P15" s="9"/>
-      <c r="Q15" s="20"/>
-      <c r="R15" s="73"/>
+      <c r="E15" s="113" t="s">
+        <v>184</v>
+      </c>
+      <c r="F15" s="111" t="s">
+        <v>186</v>
+      </c>
+      <c r="G15" s="112" t="s">
+        <v>129</v>
+      </c>
+      <c r="H15" s="112" t="s">
+        <v>132</v>
+      </c>
+      <c r="I15" s="112" t="s">
+        <v>124</v>
+      </c>
+      <c r="J15" s="112" t="s">
+        <v>193</v>
+      </c>
+      <c r="K15" s="112" t="s">
+        <v>196</v>
+      </c>
+      <c r="L15" s="112" t="s">
+        <v>131</v>
+      </c>
+      <c r="M15" s="114" t="str">
+        <f>CONCATENATE(J15,K15,L15)</f>
+        <v>=S2+MS2.CC1-Q67001</v>
+      </c>
+      <c r="N15" s="115" t="s">
+        <v>24</v>
+      </c>
+      <c r="O15" s="116" t="s">
+        <v>37</v>
+      </c>
+      <c r="P15" s="117" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q15" s="118">
+        <v>0</v>
+      </c>
+      <c r="R15" s="119" t="s">
+        <v>6</v>
+      </c>
       <c r="S15" s="74"/>
       <c r="T15" s="74"/>
-      <c r="U15" s="74"/>
+      <c r="U15" s="74" t="s">
+        <v>198</v>
+      </c>
       <c r="V15" s="10"/>
     </row>
     <row r="16" spans="1:22" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -5777,26 +6089,54 @@
       <c r="B16" s="51"/>
       <c r="C16" s="6"/>
       <c r="D16" s="32"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="N16" s="49"/>
-      <c r="O16" s="8"/>
-      <c r="P16" s="9"/>
-      <c r="Q16" s="20"/>
-      <c r="R16" s="73"/>
+      <c r="E16" s="113" t="s">
+        <v>183</v>
+      </c>
+      <c r="F16" s="111" t="s">
+        <v>187</v>
+      </c>
+      <c r="G16" s="112" t="s">
+        <v>138</v>
+      </c>
+      <c r="H16" s="112" t="s">
+        <v>130</v>
+      </c>
+      <c r="I16" s="112" t="s">
+        <v>123</v>
+      </c>
+      <c r="J16" s="112" t="s">
+        <v>193</v>
+      </c>
+      <c r="K16" s="112" t="s">
+        <v>194</v>
+      </c>
+      <c r="L16" s="112" t="s">
+        <v>141</v>
+      </c>
+      <c r="M16" s="114" t="str">
+        <f>CONCATENATE(J16,K16,L16)</f>
+        <v>=S2+SG3-B1</v>
+      </c>
+      <c r="N16" s="115" t="s">
+        <v>23</v>
+      </c>
+      <c r="O16" s="116" t="s">
+        <v>37</v>
+      </c>
+      <c r="P16" s="117" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q16" s="118">
+        <v>1</v>
+      </c>
+      <c r="R16" s="119" t="s">
+        <v>6</v>
+      </c>
       <c r="S16" s="74"/>
       <c r="T16" s="74"/>
-      <c r="U16" s="74"/>
+      <c r="U16" s="74" t="s">
+        <v>198</v>
+      </c>
       <c r="V16" s="10"/>
     </row>
     <row r="17" spans="1:22" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -5804,26 +6144,54 @@
       <c r="B17" s="51"/>
       <c r="C17" s="6"/>
       <c r="D17" s="32"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="N17" s="49"/>
-      <c r="O17" s="8"/>
-      <c r="P17" s="9"/>
-      <c r="Q17" s="20"/>
-      <c r="R17" s="73"/>
+      <c r="E17" s="113" t="s">
+        <v>183</v>
+      </c>
+      <c r="F17" s="111" t="s">
+        <v>188</v>
+      </c>
+      <c r="G17" s="112" t="s">
+        <v>138</v>
+      </c>
+      <c r="H17" s="112" t="s">
+        <v>134</v>
+      </c>
+      <c r="I17" s="112" t="s">
+        <v>123</v>
+      </c>
+      <c r="J17" s="112" t="s">
+        <v>193</v>
+      </c>
+      <c r="K17" s="112" t="s">
+        <v>195</v>
+      </c>
+      <c r="L17" s="112" t="s">
+        <v>141</v>
+      </c>
+      <c r="M17" s="114" t="str">
+        <f t="shared" ref="M17" si="4">CONCATENATE(J17,K17,L17)</f>
+        <v>=S2+SG4-B1</v>
+      </c>
+      <c r="N17" s="115" t="s">
+        <v>137</v>
+      </c>
+      <c r="O17" s="116" t="s">
+        <v>37</v>
+      </c>
+      <c r="P17" s="117" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q17" s="118">
+        <v>1</v>
+      </c>
+      <c r="R17" s="119" t="s">
+        <v>6</v>
+      </c>
       <c r="S17" s="74"/>
       <c r="T17" s="74"/>
-      <c r="U17" s="74"/>
+      <c r="U17" s="74" t="s">
+        <v>198</v>
+      </c>
       <c r="V17" s="10"/>
     </row>
     <row r="18" spans="1:22" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -5831,53 +6199,115 @@
       <c r="B18" s="51"/>
       <c r="C18" s="6"/>
       <c r="D18" s="32"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="N18" s="49"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="9"/>
-      <c r="Q18" s="20"/>
-      <c r="R18" s="73"/>
-      <c r="S18" s="74"/>
-      <c r="T18" s="74"/>
-      <c r="U18" s="74"/>
-      <c r="V18" s="10"/>
+      <c r="E18" s="113" t="s">
+        <v>184</v>
+      </c>
+      <c r="F18" s="101" t="s">
+        <v>189</v>
+      </c>
+      <c r="G18" s="112" t="s">
+        <v>129</v>
+      </c>
+      <c r="H18" s="112" t="s">
+        <v>130</v>
+      </c>
+      <c r="I18" s="112" t="s">
+        <v>121</v>
+      </c>
+      <c r="J18" s="112" t="s">
+        <v>193</v>
+      </c>
+      <c r="K18" s="112" t="s">
+        <v>197</v>
+      </c>
+      <c r="L18" s="112" t="s">
+        <v>164</v>
+      </c>
+      <c r="M18" s="114" t="str">
+        <f>CONCATENATE(J18,K18,L18)</f>
+        <v>=S2+PC2.CC1-X80101</v>
+      </c>
+      <c r="N18" s="115" t="s">
+        <v>22</v>
+      </c>
+      <c r="O18" s="116" t="s">
+        <v>37</v>
+      </c>
+      <c r="P18" s="117" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q18" s="118">
+        <v>0</v>
+      </c>
+      <c r="R18" s="119" t="s">
+        <v>6</v>
+      </c>
+      <c r="S18" s="74" t="s">
+        <v>198</v>
+      </c>
+      <c r="T18" s="74" t="s">
+        <v>198</v>
+      </c>
+      <c r="U18" s="74" t="s">
+        <v>198</v>
+      </c>
+      <c r="V18" s="10" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="19" spans="1:22" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" s="51"/>
       <c r="C19" s="6"/>
       <c r="D19" s="32"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="65" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="N19" s="49"/>
-      <c r="O19" s="8"/>
-      <c r="P19" s="9"/>
-      <c r="Q19" s="20"/>
-      <c r="R19" s="73"/>
+      <c r="E19" s="113" t="s">
+        <v>184</v>
+      </c>
+      <c r="F19" s="111" t="s">
+        <v>190</v>
+      </c>
+      <c r="G19" s="112" t="s">
+        <v>129</v>
+      </c>
+      <c r="H19" s="112" t="s">
+        <v>134</v>
+      </c>
+      <c r="I19" s="112" t="s">
+        <v>168</v>
+      </c>
+      <c r="J19" s="112" t="s">
+        <v>193</v>
+      </c>
+      <c r="K19" s="112" t="s">
+        <v>196</v>
+      </c>
+      <c r="L19" s="112" t="s">
+        <v>136</v>
+      </c>
+      <c r="M19" s="114" t="str">
+        <f t="shared" ref="M19:M21" si="5">CONCATENATE(J19,K19,L19)</f>
+        <v>=S2+MS2.CC1-S67002</v>
+      </c>
+      <c r="N19" s="115" t="s">
+        <v>36</v>
+      </c>
+      <c r="O19" s="116" t="s">
+        <v>37</v>
+      </c>
+      <c r="P19" s="117" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q19" s="118">
+        <v>0</v>
+      </c>
+      <c r="R19" s="119" t="s">
+        <v>6</v>
+      </c>
       <c r="S19" s="74"/>
       <c r="T19" s="74"/>
-      <c r="U19" s="74"/>
+      <c r="U19" s="98" t="s">
+        <v>150</v>
+      </c>
       <c r="V19" s="10"/>
     </row>
     <row r="20" spans="1:22" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -5885,54 +6315,102 @@
       <c r="B20" s="51"/>
       <c r="C20" s="6"/>
       <c r="D20" s="32"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="N20" s="49"/>
-      <c r="O20" s="8"/>
-      <c r="P20" s="9"/>
-      <c r="Q20" s="20"/>
-      <c r="R20" s="73"/>
+      <c r="E20" s="113" t="s">
+        <v>184</v>
+      </c>
+      <c r="F20" s="111" t="s">
+        <v>191</v>
+      </c>
+      <c r="G20" s="112" t="s">
+        <v>129</v>
+      </c>
+      <c r="H20" s="112" t="s">
+        <v>134</v>
+      </c>
+      <c r="I20" s="112" t="s">
+        <v>168</v>
+      </c>
+      <c r="J20" s="112" t="s">
+        <v>193</v>
+      </c>
+      <c r="K20" s="112" t="s">
+        <v>196</v>
+      </c>
+      <c r="L20" s="120" t="s">
+        <v>170</v>
+      </c>
+      <c r="M20" s="114" t="str">
+        <f t="shared" si="5"/>
+        <v>=S2+MS2.CC1-S67008</v>
+      </c>
+      <c r="N20" s="115" t="s">
+        <v>36</v>
+      </c>
+      <c r="O20" s="116" t="s">
+        <v>37</v>
+      </c>
+      <c r="P20" s="117" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q20" s="118">
+        <v>0</v>
+      </c>
+      <c r="R20" s="119" t="s">
+        <v>6</v>
+      </c>
       <c r="S20" s="74"/>
       <c r="T20" s="74"/>
       <c r="U20" s="74"/>
-      <c r="V20" s="10"/>
+      <c r="V20" s="98" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="21" spans="1:22" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
       <c r="B21" s="51"/>
       <c r="C21" s="6"/>
       <c r="D21" s="32"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="N21" s="49"/>
-      <c r="O21" s="8"/>
-      <c r="P21" s="9"/>
-      <c r="Q21" s="20"/>
-      <c r="R21" s="73"/>
+      <c r="E21" s="113" t="s">
+        <v>184</v>
+      </c>
+      <c r="F21" s="111" t="s">
+        <v>192</v>
+      </c>
+      <c r="G21" s="112" t="s">
+        <v>129</v>
+      </c>
+      <c r="H21" s="112" t="s">
+        <v>172</v>
+      </c>
+      <c r="I21" s="112" t="s">
+        <v>173</v>
+      </c>
+      <c r="J21" s="112" t="s">
+        <v>193</v>
+      </c>
+      <c r="K21" s="112" t="s">
+        <v>196</v>
+      </c>
+      <c r="L21" s="112" t="s">
+        <v>174</v>
+      </c>
+      <c r="M21" s="114" t="str">
+        <f t="shared" si="5"/>
+        <v>=S2+MS2.CC1-X40001</v>
+      </c>
+      <c r="N21" s="115"/>
+      <c r="O21" s="116"/>
+      <c r="P21" s="117"/>
+      <c r="Q21" s="118"/>
+      <c r="R21" s="119"/>
       <c r="S21" s="74"/>
       <c r="T21" s="74"/>
-      <c r="U21" s="74"/>
-      <c r="V21" s="10"/>
+      <c r="U21" s="74" t="s">
+        <v>198</v>
+      </c>
+      <c r="V21" s="10" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="22" spans="1:22" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
@@ -5948,7 +6426,7 @@
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
       <c r="M22" s="65" t="str">
-        <f t="shared" ref="M22:M23" si="4">CONCATENATE(J22,K22,L22)</f>
+        <f t="shared" ref="M22:M23" si="6">CONCATENATE(J22,K22,L22)</f>
         <v/>
       </c>
       <c r="N22" s="49"/>
@@ -5975,7 +6453,7 @@
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
       <c r="M23" s="65" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N23" s="49"/>
@@ -6041,51 +6519,61 @@
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="A1:A3 A5:A1048576">
-    <cfRule type="containsText" dxfId="11" priority="28" operator="containsText" text="Not Tested">
+    <cfRule type="containsText" dxfId="13" priority="30" operator="containsText" text="Not Tested">
       <formula>NOT(ISERROR(SEARCH("Not Tested",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A3">
-    <cfRule type="containsText" dxfId="10" priority="24" operator="containsText" text="Removed">
+    <cfRule type="containsText" dxfId="12" priority="26" operator="containsText" text="Removed">
       <formula>NOT(ISERROR(SEARCH("Removed",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="25" operator="containsText" text="NOK">
+    <cfRule type="containsText" dxfId="11" priority="27" operator="containsText" text="NOK">
       <formula>NOT(ISERROR(SEARCH("NOK",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="26" operator="containsText" text="Bypass">
+    <cfRule type="containsText" dxfId="10" priority="28" operator="containsText" text="Bypass">
       <formula>NOT(ISERROR(SEARCH("Bypass",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="27" operator="containsText" text="OK">
+    <cfRule type="containsText" dxfId="9" priority="29" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:A1048576">
-    <cfRule type="containsText" dxfId="6" priority="14" operator="containsText" text="Removed">
+    <cfRule type="containsText" dxfId="8" priority="16" operator="containsText" text="Removed">
       <formula>NOT(ISERROR(SEARCH("Removed",A5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="15" operator="containsText" text="NOK">
+    <cfRule type="containsText" dxfId="7" priority="17" operator="containsText" text="NOK">
       <formula>NOT(ISERROR(SEARCH("NOK",A5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="16" operator="containsText" text="Bypass">
+    <cfRule type="containsText" dxfId="6" priority="18" operator="containsText" text="Bypass">
       <formula>NOT(ISERROR(SEARCH("Bypass",A5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:C1048576">
-    <cfRule type="containsText" dxfId="3" priority="21" operator="containsText" text="OK">
+    <cfRule type="containsText" dxfId="5" priority="23" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",A5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:B1048576">
-    <cfRule type="containsText" dxfId="2" priority="12" operator="containsText" text="NOK">
+    <cfRule type="containsText" dxfId="4" priority="14" operator="containsText" text="NOK">
       <formula>NOT(ISERROR(SEARCH("NOK",B5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5:C1048576">
-    <cfRule type="containsText" dxfId="1" priority="9" operator="containsText" text="Not Verified">
+    <cfRule type="containsText" dxfId="3" priority="11" operator="containsText" text="Not Verified">
       <formula>NOT(ISERROR(SEARCH("Not Verified",C5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="10" operator="containsText" text="NOK">
+    <cfRule type="containsText" dxfId="2" priority="12" operator="containsText" text="NOK">
       <formula>NOT(ISERROR(SEARCH("NOK",C5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L11">
+    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
+      <formula>#REF!="PA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L20">
+    <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
+      <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
@@ -6128,10 +6616,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="240"/>
-      <c r="B1" s="240"/>
-      <c r="C1" s="240"/>
-      <c r="D1" s="240"/>
+      <c r="A1" s="252"/>
+      <c r="B1" s="252"/>
+      <c r="C1" s="252"/>
+      <c r="D1" s="252"/>
     </row>
     <row r="2" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="103" t="s">
@@ -6163,41 +6651,37 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B4" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="D4" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="D4" s="12" t="s">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="D5" s="12" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="18"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="72"/>
       <c r="B6" s="17"/>
       <c r="C6" s="12"/>
       <c r="D6" s="18"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="72"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="18"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="72"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="18"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="72"/>
@@ -6534,7 +7018,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet7">
-    <tabColor theme="8" tint="0.59999389629810485"/>
+    <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:D43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6546,10 +7030,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="240"/>
-      <c r="B1" s="240"/>
-      <c r="C1" s="240"/>
-      <c r="D1" s="240"/>
+      <c r="A1" s="252"/>
+      <c r="B1" s="252"/>
+      <c r="C1" s="252"/>
+      <c r="D1" s="252"/>
     </row>
     <row r="2" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="103" t="s">
@@ -6581,41 +7065,37 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C4" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="D4" s="66" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="B5" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="D4" s="66" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="18"/>
+      <c r="C5" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="15"/>
       <c r="B6" s="17"/>
       <c r="C6" s="12"/>
       <c r="D6" s="18"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="18"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="15"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="18"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="15"/>
@@ -6887,16 +7367,32 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
-      <c r="B4" s="72"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="66"/>
+      <c r="A4" s="110" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" s="110" t="s">
+        <v>175</v>
+      </c>
+      <c r="C4" s="100" t="s">
+        <v>178</v>
+      </c>
+      <c r="D4" s="100" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
-      <c r="B5" s="72"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="66"/>
+      <c r="A5" s="110" t="s">
+        <v>181</v>
+      </c>
+      <c r="B5" s="110" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" s="100" t="s">
+        <v>182</v>
+      </c>
+      <c r="D5" s="100" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="72"/>
@@ -7642,16 +8138,32 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
-      <c r="B4" s="72"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="66"/>
+      <c r="A4" s="110" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" s="110" t="s">
+        <v>175</v>
+      </c>
+      <c r="C4" s="100" t="s">
+        <v>178</v>
+      </c>
+      <c r="D4" s="100" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
-      <c r="B5" s="72"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="66"/>
+      <c r="A5" s="110" t="s">
+        <v>177</v>
+      </c>
+      <c r="B5" s="110" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" s="100" t="s">
+        <v>179</v>
+      </c>
+      <c r="D5" s="100" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="72"/>
@@ -8364,37 +8876,37 @@
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="266" t="s">
+      <c r="A2" s="278" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="269" t="s">
+      <c r="B2" s="281" t="s">
         <v>113</v>
       </c>
-      <c r="C2" s="270"/>
+      <c r="C2" s="282"/>
     </row>
     <row r="3" spans="1:4" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="267"/>
-      <c r="B3" s="271"/>
-      <c r="C3" s="272"/>
+      <c r="A3" s="279"/>
+      <c r="B3" s="283"/>
+      <c r="C3" s="284"/>
     </row>
     <row r="4" spans="1:4" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="268"/>
-      <c r="B4" s="273"/>
-      <c r="C4" s="274"/>
+      <c r="A4" s="280"/>
+      <c r="B4" s="285"/>
+      <c r="C4" s="286"/>
     </row>
     <row r="5" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="1:4" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="68" t="s">
         <v>110</v>
       </c>
-      <c r="B6" s="248" t="s">
+      <c r="B6" s="260" t="s">
         <v>112</v>
       </c>
-      <c r="C6" s="249"/>
+      <c r="C6" s="261"/>
     </row>
     <row r="7" spans="1:4" ht="34.9" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="275"/>
-      <c r="B7" s="246" t="s">
+      <c r="A7" s="287"/>
+      <c r="B7" s="258" t="s">
         <v>27</v>
       </c>
       <c r="C7" s="36" t="s">
@@ -8403,40 +8915,40 @@
       <c r="D7" s="69"/>
     </row>
     <row r="8" spans="1:4" ht="34.9" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="242"/>
-      <c r="B8" s="250"/>
+      <c r="A8" s="254"/>
+      <c r="B8" s="262"/>
       <c r="C8" s="37" t="s">
         <v>29</v>
       </c>
       <c r="D8" s="69"/>
     </row>
     <row r="9" spans="1:4" ht="34.9" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="242"/>
-      <c r="B9" s="250"/>
+      <c r="A9" s="254"/>
+      <c r="B9" s="262"/>
       <c r="C9" s="37" t="s">
         <v>52</v>
       </c>
       <c r="D9" s="69"/>
     </row>
     <row r="10" spans="1:4" ht="34.9" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="242"/>
-      <c r="B10" s="250"/>
+      <c r="A10" s="254"/>
+      <c r="B10" s="262"/>
       <c r="C10" s="37" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="69"/>
     </row>
     <row r="11" spans="1:4" ht="34.9" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="242"/>
-      <c r="B11" s="247"/>
+      <c r="A11" s="254"/>
+      <c r="B11" s="259"/>
       <c r="C11" s="38" t="s">
         <v>31</v>
       </c>
       <c r="D11" s="69"/>
     </row>
     <row r="12" spans="1:4" ht="34.9" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="242"/>
-      <c r="B12" s="251" t="s">
+      <c r="A12" s="254"/>
+      <c r="B12" s="263" t="s">
         <v>32</v>
       </c>
       <c r="C12" s="36" t="s">
@@ -8444,15 +8956,15 @@
       </c>
     </row>
     <row r="13" spans="1:4" ht="34.9" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="242"/>
-      <c r="B13" s="252"/>
+      <c r="A13" s="254"/>
+      <c r="B13" s="264"/>
       <c r="C13" s="39" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="34.9" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="242"/>
-      <c r="B14" s="253" t="s">
+      <c r="A14" s="254"/>
+      <c r="B14" s="265" t="s">
         <v>39</v>
       </c>
       <c r="C14" s="36" t="s">
@@ -8460,22 +8972,22 @@
       </c>
     </row>
     <row r="15" spans="1:4" ht="34.9" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="242"/>
-      <c r="B15" s="254"/>
+      <c r="A15" s="254"/>
+      <c r="B15" s="266"/>
       <c r="C15" s="37" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="34.9" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="242"/>
-      <c r="B16" s="254"/>
+      <c r="A16" s="254"/>
+      <c r="B16" s="266"/>
       <c r="C16" s="44" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="34.9" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="243"/>
-      <c r="B17" s="255"/>
+      <c r="A17" s="255"/>
+      <c r="B17" s="267"/>
       <c r="C17" s="39" t="s">
         <v>33</v>
       </c>
@@ -8485,14 +8997,14 @@
       <c r="A19" s="67" t="s">
         <v>114</v>
       </c>
-      <c r="B19" s="248" t="s">
+      <c r="B19" s="260" t="s">
         <v>48</v>
       </c>
-      <c r="C19" s="249"/>
+      <c r="C19" s="261"/>
     </row>
     <row r="20" spans="1:12" ht="39" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="241"/>
-      <c r="B20" s="256" t="s">
+      <c r="A20" s="253"/>
+      <c r="B20" s="268" t="s">
         <v>27</v>
       </c>
       <c r="C20" s="36" t="s">
@@ -8500,22 +9012,22 @@
       </c>
     </row>
     <row r="21" spans="1:12" ht="39" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="242"/>
-      <c r="B21" s="257"/>
+      <c r="A21" s="254"/>
+      <c r="B21" s="269"/>
       <c r="C21" s="37" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="39" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="242"/>
-      <c r="B22" s="258"/>
+      <c r="A22" s="254"/>
+      <c r="B22" s="270"/>
       <c r="C22" s="39" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="39" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="242"/>
-      <c r="B23" s="251" t="s">
+      <c r="A23" s="254"/>
+      <c r="B23" s="263" t="s">
         <v>32</v>
       </c>
       <c r="C23" s="36" t="s">
@@ -8523,22 +9035,22 @@
       </c>
     </row>
     <row r="24" spans="1:12" ht="39" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="242"/>
-      <c r="B24" s="259"/>
+      <c r="A24" s="254"/>
+      <c r="B24" s="271"/>
       <c r="C24" s="37" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="39" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="242"/>
-      <c r="B25" s="252"/>
+      <c r="A25" s="254"/>
+      <c r="B25" s="264"/>
       <c r="C25" s="38" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="39" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="242"/>
-      <c r="B26" s="254" t="s">
+      <c r="A26" s="254"/>
+      <c r="B26" s="266" t="s">
         <v>39</v>
       </c>
       <c r="C26" s="37" t="s">
@@ -8546,70 +9058,70 @@
       </c>
     </row>
     <row r="27" spans="1:12" ht="39" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="242"/>
-      <c r="B27" s="254"/>
+      <c r="A27" s="254"/>
+      <c r="B27" s="266"/>
       <c r="C27" s="37" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="39" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="242"/>
-      <c r="B28" s="254"/>
+      <c r="A28" s="254"/>
+      <c r="B28" s="266"/>
       <c r="C28" s="37" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="39" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="242"/>
-      <c r="B29" s="254"/>
+      <c r="A29" s="254"/>
+      <c r="B29" s="266"/>
       <c r="C29" s="37" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="39" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="242"/>
-      <c r="B30" s="254"/>
+      <c r="A30" s="254"/>
+      <c r="B30" s="266"/>
       <c r="C30" s="40" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="39" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="242"/>
-      <c r="B31" s="254"/>
+      <c r="A31" s="254"/>
+      <c r="B31" s="266"/>
       <c r="C31" s="37" t="s">
         <v>95</v>
       </c>
       <c r="D31" s="102" t="s">
         <v>49</v>
       </c>
-      <c r="G31" s="260" t="s">
+      <c r="G31" s="272" t="s">
         <v>98</v>
       </c>
-      <c r="H31" s="261"/>
-      <c r="I31" s="261"/>
-      <c r="J31" s="262"/>
+      <c r="H31" s="273"/>
+      <c r="I31" s="273"/>
+      <c r="J31" s="274"/>
       <c r="K31" s="56"/>
       <c r="L31" s="56"/>
     </row>
     <row r="32" spans="1:12" ht="39" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="242"/>
-      <c r="B32" s="254"/>
+      <c r="A32" s="254"/>
+      <c r="B32" s="266"/>
       <c r="C32" s="37" t="s">
         <v>94</v>
       </c>
       <c r="D32" s="102" t="s">
         <v>49</v>
       </c>
-      <c r="G32" s="263"/>
-      <c r="H32" s="264"/>
-      <c r="I32" s="264"/>
-      <c r="J32" s="265"/>
+      <c r="G32" s="275"/>
+      <c r="H32" s="276"/>
+      <c r="I32" s="276"/>
+      <c r="J32" s="277"/>
       <c r="K32" s="56"/>
       <c r="L32" s="56"/>
     </row>
     <row r="33" spans="1:3" ht="39" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="243"/>
-      <c r="B33" s="255"/>
+      <c r="A33" s="255"/>
+      <c r="B33" s="267"/>
       <c r="C33" s="41" t="s">
         <v>53</v>
       </c>
@@ -8619,14 +9131,14 @@
       <c r="A35" s="67" t="s">
         <v>109</v>
       </c>
-      <c r="B35" s="248" t="s">
+      <c r="B35" s="260" t="s">
         <v>54</v>
       </c>
-      <c r="C35" s="249"/>
+      <c r="C35" s="261"/>
     </row>
     <row r="36" spans="1:3" ht="28.15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="241"/>
-      <c r="B36" s="246" t="s">
+      <c r="A36" s="253"/>
+      <c r="B36" s="258" t="s">
         <v>27</v>
       </c>
       <c r="C36" s="36" t="s">
@@ -8634,21 +9146,21 @@
       </c>
     </row>
     <row r="37" spans="1:3" ht="28.15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="242"/>
-      <c r="B37" s="257"/>
+      <c r="A37" s="254"/>
+      <c r="B37" s="269"/>
       <c r="C37" s="37" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="28.15" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="242"/>
-      <c r="B38" s="247"/>
+      <c r="A38" s="254"/>
+      <c r="B38" s="259"/>
       <c r="C38" s="57" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="28.15" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="242"/>
+      <c r="A39" s="254"/>
       <c r="B39" s="42" t="s">
         <v>32</v>
       </c>
@@ -8657,8 +9169,8 @@
       </c>
     </row>
     <row r="40" spans="1:3" ht="28.15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="242"/>
-      <c r="B40" s="244" t="s">
+      <c r="A40" s="254"/>
+      <c r="B40" s="256" t="s">
         <v>39</v>
       </c>
       <c r="C40" s="36" t="s">
@@ -8666,8 +9178,8 @@
       </c>
     </row>
     <row r="41" spans="1:3" ht="38.450000000000003" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="243"/>
-      <c r="B41" s="245"/>
+      <c r="A41" s="255"/>
+      <c r="B41" s="257"/>
       <c r="C41" s="39" t="s">
         <v>99</v>
       </c>
@@ -8677,14 +9189,14 @@
       <c r="A43" s="67" t="s">
         <v>108</v>
       </c>
-      <c r="B43" s="248" t="s">
+      <c r="B43" s="260" t="s">
         <v>58</v>
       </c>
-      <c r="C43" s="249"/>
+      <c r="C43" s="261"/>
     </row>
     <row r="44" spans="1:3" ht="24" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="241"/>
-      <c r="B44" s="246" t="s">
+      <c r="A44" s="253"/>
+      <c r="B44" s="258" t="s">
         <v>27</v>
       </c>
       <c r="C44" s="36" t="s">
@@ -8692,14 +9204,14 @@
       </c>
     </row>
     <row r="45" spans="1:3" ht="24" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="242"/>
-      <c r="B45" s="247"/>
+      <c r="A45" s="254"/>
+      <c r="B45" s="259"/>
       <c r="C45" s="39" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="24" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="242"/>
+      <c r="A46" s="254"/>
       <c r="B46" s="42" t="s">
         <v>32</v>
       </c>
@@ -8708,8 +9220,8 @@
       </c>
     </row>
     <row r="47" spans="1:3" ht="24" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="242"/>
-      <c r="B47" s="244" t="s">
+      <c r="A47" s="254"/>
+      <c r="B47" s="256" t="s">
         <v>39</v>
       </c>
       <c r="C47" s="36" t="s">
@@ -8717,8 +9229,8 @@
       </c>
     </row>
     <row r="48" spans="1:3" ht="24" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="243"/>
-      <c r="B48" s="245"/>
+      <c r="A48" s="255"/>
+      <c r="B48" s="257"/>
       <c r="C48" s="39" t="s">
         <v>106</v>
       </c>
@@ -8769,33 +9281,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="276" t="s">
+      <c r="B1" s="288" t="s">
         <v>75</v>
       </c>
-      <c r="C1" s="277"/>
-      <c r="D1" s="277"/>
-      <c r="E1" s="277"/>
-      <c r="F1" s="277"/>
-      <c r="G1" s="277"/>
-      <c r="H1" s="278"/>
+      <c r="C1" s="289"/>
+      <c r="D1" s="289"/>
+      <c r="E1" s="289"/>
+      <c r="F1" s="289"/>
+      <c r="G1" s="289"/>
+      <c r="H1" s="290"/>
     </row>
     <row r="2" spans="2:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="279"/>
-      <c r="C2" s="280"/>
-      <c r="D2" s="280"/>
-      <c r="E2" s="280"/>
-      <c r="F2" s="280"/>
-      <c r="G2" s="280"/>
-      <c r="H2" s="281"/>
+      <c r="B2" s="291"/>
+      <c r="C2" s="292"/>
+      <c r="D2" s="292"/>
+      <c r="E2" s="292"/>
+      <c r="F2" s="292"/>
+      <c r="G2" s="292"/>
+      <c r="H2" s="293"/>
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="282"/>
-      <c r="C3" s="283"/>
-      <c r="D3" s="283"/>
-      <c r="E3" s="283"/>
-      <c r="F3" s="283"/>
-      <c r="G3" s="283"/>
-      <c r="H3" s="284"/>
+      <c r="B3" s="294"/>
+      <c r="C3" s="295"/>
+      <c r="D3" s="295"/>
+      <c r="E3" s="295"/>
+      <c r="F3" s="295"/>
+      <c r="G3" s="295"/>
+      <c r="H3" s="296"/>
     </row>
     <row r="4" spans="2:8" ht="32.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="46" t="s">
@@ -8804,121 +9316,121 @@
       <c r="C4" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="306" t="s">
+      <c r="D4" s="318" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="307"/>
-      <c r="F4" s="308"/>
-      <c r="G4" s="306" t="s">
+      <c r="E4" s="319"/>
+      <c r="F4" s="320"/>
+      <c r="G4" s="318" t="s">
         <v>63</v>
       </c>
-      <c r="H4" s="308"/>
+      <c r="H4" s="320"/>
     </row>
     <row r="5" spans="2:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="303" t="s">
+      <c r="B5" s="315" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="309"/>
-      <c r="D5" s="310"/>
-      <c r="E5" s="310"/>
-      <c r="F5" s="310"/>
-      <c r="G5" s="310"/>
-      <c r="H5" s="311"/>
+      <c r="C5" s="321"/>
+      <c r="D5" s="322"/>
+      <c r="E5" s="322"/>
+      <c r="F5" s="322"/>
+      <c r="G5" s="322"/>
+      <c r="H5" s="323"/>
     </row>
     <row r="6" spans="2:8" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="304"/>
-      <c r="C6" s="312"/>
-      <c r="D6" s="313"/>
-      <c r="E6" s="313"/>
-      <c r="F6" s="313"/>
-      <c r="G6" s="313"/>
-      <c r="H6" s="314"/>
+      <c r="B6" s="316"/>
+      <c r="C6" s="324"/>
+      <c r="D6" s="325"/>
+      <c r="E6" s="325"/>
+      <c r="F6" s="325"/>
+      <c r="G6" s="325"/>
+      <c r="H6" s="326"/>
     </row>
     <row r="7" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="305"/>
-      <c r="C7" s="315"/>
-      <c r="D7" s="316"/>
-      <c r="E7" s="316"/>
-      <c r="F7" s="316"/>
-      <c r="G7" s="316"/>
-      <c r="H7" s="317"/>
+      <c r="B7" s="317"/>
+      <c r="C7" s="327"/>
+      <c r="D7" s="328"/>
+      <c r="E7" s="328"/>
+      <c r="F7" s="328"/>
+      <c r="G7" s="328"/>
+      <c r="H7" s="329"/>
     </row>
     <row r="8" spans="2:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="318"/>
-      <c r="D8" s="319"/>
-      <c r="E8" s="320" t="s">
+      <c r="C8" s="330"/>
+      <c r="D8" s="331"/>
+      <c r="E8" s="332" t="s">
         <v>74</v>
       </c>
-      <c r="F8" s="321"/>
-      <c r="G8" s="322"/>
+      <c r="F8" s="333"/>
+      <c r="G8" s="334"/>
       <c r="H8" s="55" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="303" t="s">
+      <c r="B9" s="315" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="323"/>
-      <c r="D9" s="324"/>
-      <c r="E9" s="324"/>
-      <c r="F9" s="324"/>
-      <c r="G9" s="324"/>
-      <c r="H9" s="325"/>
+      <c r="C9" s="335"/>
+      <c r="D9" s="336"/>
+      <c r="E9" s="336"/>
+      <c r="F9" s="336"/>
+      <c r="G9" s="336"/>
+      <c r="H9" s="337"/>
     </row>
     <row r="10" spans="2:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="304"/>
-      <c r="C10" s="326"/>
-      <c r="D10" s="327"/>
-      <c r="E10" s="327"/>
-      <c r="F10" s="327"/>
-      <c r="G10" s="327"/>
-      <c r="H10" s="328"/>
+      <c r="B10" s="316"/>
+      <c r="C10" s="338"/>
+      <c r="D10" s="339"/>
+      <c r="E10" s="339"/>
+      <c r="F10" s="339"/>
+      <c r="G10" s="339"/>
+      <c r="H10" s="340"/>
     </row>
     <row r="11" spans="2:8" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="305"/>
-      <c r="C11" s="329"/>
-      <c r="D11" s="330"/>
-      <c r="E11" s="330"/>
-      <c r="F11" s="330"/>
-      <c r="G11" s="330"/>
-      <c r="H11" s="331"/>
+      <c r="B11" s="317"/>
+      <c r="C11" s="341"/>
+      <c r="D11" s="342"/>
+      <c r="E11" s="342"/>
+      <c r="F11" s="342"/>
+      <c r="G11" s="342"/>
+      <c r="H11" s="343"/>
     </row>
     <row r="12" spans="2:8" ht="22.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="294" t="s">
+      <c r="C12" s="306" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="295"/>
-      <c r="E12" s="296"/>
-      <c r="F12" s="285"/>
-      <c r="G12" s="286"/>
-      <c r="H12" s="287"/>
+      <c r="D12" s="307"/>
+      <c r="E12" s="308"/>
+      <c r="F12" s="297"/>
+      <c r="G12" s="298"/>
+      <c r="H12" s="299"/>
     </row>
     <row r="13" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="303" t="s">
+      <c r="B13" s="315" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="297"/>
-      <c r="D13" s="298"/>
-      <c r="E13" s="299"/>
-      <c r="F13" s="288"/>
-      <c r="G13" s="289"/>
-      <c r="H13" s="290"/>
+      <c r="C13" s="309"/>
+      <c r="D13" s="310"/>
+      <c r="E13" s="311"/>
+      <c r="F13" s="300"/>
+      <c r="G13" s="301"/>
+      <c r="H13" s="302"/>
     </row>
     <row r="14" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="305"/>
-      <c r="C14" s="300"/>
-      <c r="D14" s="301"/>
-      <c r="E14" s="302"/>
-      <c r="F14" s="291"/>
-      <c r="G14" s="292"/>
-      <c r="H14" s="293"/>
+      <c r="B14" s="317"/>
+      <c r="C14" s="312"/>
+      <c r="D14" s="313"/>
+      <c r="E14" s="314"/>
+      <c r="F14" s="303"/>
+      <c r="G14" s="304"/>
+      <c r="H14" s="305"/>
     </row>
   </sheetData>
   <mergeCells count="13">

--- a/Shared/DocumentsValidationData/Passing/8XXX_Cause and Effect Matrix_R0.0_ValidationTemplate.xlsx
+++ b/Shared/DocumentsValidationData/Passing/8XXX_Cause and Effect Matrix_R0.0_ValidationTemplate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Source\Repos\_Openn2\Shared\DocumentsValidationData\Passing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C2ABE88-CE84-4A08-8E04-7137F7AE5F28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E02157FF-0B50-4C57-B459-06345155F1DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17790" tabRatio="713" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="12855" tabRatio="713" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COVER" sheetId="1" r:id="rId1"/>
@@ -861,15 +861,15 @@
   </si>
   <si>
     <t>Area 2
+(Conveyors North)</t>
+  </si>
+  <si>
+    <t>Area 3
 (Conveyors East)</t>
   </si>
   <si>
-    <t>Area 2
+    <t>Area 4
 (Conveyors West)</t>
-  </si>
-  <si>
-    <t>Area 2
-(Conveyors North)</t>
   </si>
 </sst>
 </file>
@@ -2603,421 +2603,478 @@
     <xf numFmtId="49" fontId="52" fillId="8" borderId="0" xfId="7" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="46" fillId="6" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="6" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="6" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="11" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="11" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="11" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="11" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="6" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="4" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="6" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="6" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="6" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="11" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="11" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="11" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="11" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="6" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3038,71 +3095,14 @@
     <xf numFmtId="0" fontId="14" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4086,279 +4086,279 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="198"/>
-      <c r="B1" s="199"/>
-      <c r="C1" s="199"/>
-      <c r="D1" s="199"/>
-      <c r="E1" s="199"/>
-      <c r="F1" s="199"/>
-      <c r="G1" s="199"/>
-      <c r="H1" s="199"/>
-      <c r="I1" s="199"/>
-      <c r="J1" s="199"/>
-      <c r="K1" s="199"/>
-      <c r="L1" s="200"/>
+      <c r="A1" s="150"/>
+      <c r="B1" s="151"/>
+      <c r="C1" s="151"/>
+      <c r="D1" s="151"/>
+      <c r="E1" s="151"/>
+      <c r="F1" s="151"/>
+      <c r="G1" s="151"/>
+      <c r="H1" s="151"/>
+      <c r="I1" s="151"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="152"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="201"/>
-      <c r="B2" s="176"/>
-      <c r="C2" s="176"/>
-      <c r="D2" s="176"/>
-      <c r="E2" s="176"/>
-      <c r="F2" s="176"/>
-      <c r="G2" s="176"/>
-      <c r="H2" s="176"/>
-      <c r="I2" s="176"/>
-      <c r="J2" s="176"/>
-      <c r="K2" s="176"/>
-      <c r="L2" s="179"/>
+      <c r="A2" s="153"/>
+      <c r="B2" s="154"/>
+      <c r="C2" s="154"/>
+      <c r="D2" s="154"/>
+      <c r="E2" s="154"/>
+      <c r="F2" s="154"/>
+      <c r="G2" s="154"/>
+      <c r="H2" s="154"/>
+      <c r="I2" s="154"/>
+      <c r="J2" s="154"/>
+      <c r="K2" s="154"/>
+      <c r="L2" s="155"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="201"/>
-      <c r="B3" s="176"/>
-      <c r="C3" s="176"/>
-      <c r="D3" s="176"/>
-      <c r="E3" s="176"/>
-      <c r="F3" s="176"/>
-      <c r="G3" s="176"/>
-      <c r="H3" s="176"/>
-      <c r="I3" s="176"/>
-      <c r="J3" s="176"/>
-      <c r="K3" s="176"/>
-      <c r="L3" s="179"/>
+      <c r="A3" s="153"/>
+      <c r="B3" s="154"/>
+      <c r="C3" s="154"/>
+      <c r="D3" s="154"/>
+      <c r="E3" s="154"/>
+      <c r="F3" s="154"/>
+      <c r="G3" s="154"/>
+      <c r="H3" s="154"/>
+      <c r="I3" s="154"/>
+      <c r="J3" s="154"/>
+      <c r="K3" s="154"/>
+      <c r="L3" s="155"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="201"/>
-      <c r="B4" s="176"/>
-      <c r="C4" s="176"/>
-      <c r="D4" s="176"/>
-      <c r="E4" s="176"/>
-      <c r="F4" s="176"/>
-      <c r="G4" s="176"/>
-      <c r="H4" s="176"/>
-      <c r="I4" s="176"/>
-      <c r="J4" s="176"/>
-      <c r="K4" s="176"/>
-      <c r="L4" s="179"/>
+      <c r="A4" s="153"/>
+      <c r="B4" s="154"/>
+      <c r="C4" s="154"/>
+      <c r="D4" s="154"/>
+      <c r="E4" s="154"/>
+      <c r="F4" s="154"/>
+      <c r="G4" s="154"/>
+      <c r="H4" s="154"/>
+      <c r="I4" s="154"/>
+      <c r="J4" s="154"/>
+      <c r="K4" s="154"/>
+      <c r="L4" s="155"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="201"/>
-      <c r="B5" s="176"/>
-      <c r="C5" s="176"/>
-      <c r="D5" s="176"/>
-      <c r="E5" s="176"/>
-      <c r="F5" s="176"/>
-      <c r="G5" s="176"/>
-      <c r="H5" s="176"/>
-      <c r="I5" s="176"/>
-      <c r="J5" s="176"/>
-      <c r="K5" s="176"/>
-      <c r="L5" s="179"/>
+      <c r="A5" s="153"/>
+      <c r="B5" s="154"/>
+      <c r="C5" s="154"/>
+      <c r="D5" s="154"/>
+      <c r="E5" s="154"/>
+      <c r="F5" s="154"/>
+      <c r="G5" s="154"/>
+      <c r="H5" s="154"/>
+      <c r="I5" s="154"/>
+      <c r="J5" s="154"/>
+      <c r="K5" s="154"/>
+      <c r="L5" s="155"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="201"/>
-      <c r="B6" s="176"/>
-      <c r="C6" s="176"/>
-      <c r="D6" s="176"/>
-      <c r="E6" s="176"/>
-      <c r="F6" s="176"/>
-      <c r="G6" s="176"/>
-      <c r="H6" s="176"/>
-      <c r="I6" s="176"/>
-      <c r="J6" s="176"/>
-      <c r="K6" s="176"/>
-      <c r="L6" s="179"/>
+      <c r="A6" s="153"/>
+      <c r="B6" s="154"/>
+      <c r="C6" s="154"/>
+      <c r="D6" s="154"/>
+      <c r="E6" s="154"/>
+      <c r="F6" s="154"/>
+      <c r="G6" s="154"/>
+      <c r="H6" s="154"/>
+      <c r="I6" s="154"/>
+      <c r="J6" s="154"/>
+      <c r="K6" s="154"/>
+      <c r="L6" s="155"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="201"/>
-      <c r="B7" s="176"/>
-      <c r="C7" s="176"/>
-      <c r="D7" s="176"/>
-      <c r="E7" s="176"/>
-      <c r="F7" s="176"/>
-      <c r="G7" s="176"/>
-      <c r="H7" s="176"/>
-      <c r="I7" s="176"/>
-      <c r="J7" s="176"/>
-      <c r="K7" s="176"/>
-      <c r="L7" s="179"/>
+      <c r="A7" s="153"/>
+      <c r="B7" s="154"/>
+      <c r="C7" s="154"/>
+      <c r="D7" s="154"/>
+      <c r="E7" s="154"/>
+      <c r="F7" s="154"/>
+      <c r="G7" s="154"/>
+      <c r="H7" s="154"/>
+      <c r="I7" s="154"/>
+      <c r="J7" s="154"/>
+      <c r="K7" s="154"/>
+      <c r="L7" s="155"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="201"/>
-      <c r="B8" s="176"/>
-      <c r="C8" s="176"/>
-      <c r="D8" s="176"/>
-      <c r="E8" s="176"/>
-      <c r="F8" s="176"/>
-      <c r="G8" s="176"/>
-      <c r="H8" s="176"/>
-      <c r="I8" s="176"/>
-      <c r="J8" s="176"/>
-      <c r="K8" s="176"/>
-      <c r="L8" s="179"/>
+      <c r="A8" s="153"/>
+      <c r="B8" s="154"/>
+      <c r="C8" s="154"/>
+      <c r="D8" s="154"/>
+      <c r="E8" s="154"/>
+      <c r="F8" s="154"/>
+      <c r="G8" s="154"/>
+      <c r="H8" s="154"/>
+      <c r="I8" s="154"/>
+      <c r="J8" s="154"/>
+      <c r="K8" s="154"/>
+      <c r="L8" s="155"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="201"/>
-      <c r="B9" s="176"/>
-      <c r="C9" s="176"/>
-      <c r="D9" s="176"/>
-      <c r="E9" s="176"/>
-      <c r="F9" s="176"/>
-      <c r="G9" s="176"/>
-      <c r="H9" s="176"/>
-      <c r="I9" s="176"/>
-      <c r="J9" s="176"/>
-      <c r="K9" s="176"/>
-      <c r="L9" s="179"/>
+      <c r="A9" s="153"/>
+      <c r="B9" s="154"/>
+      <c r="C9" s="154"/>
+      <c r="D9" s="154"/>
+      <c r="E9" s="154"/>
+      <c r="F9" s="154"/>
+      <c r="G9" s="154"/>
+      <c r="H9" s="154"/>
+      <c r="I9" s="154"/>
+      <c r="J9" s="154"/>
+      <c r="K9" s="154"/>
+      <c r="L9" s="155"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="201"/>
-      <c r="B10" s="176"/>
-      <c r="C10" s="176"/>
-      <c r="D10" s="176"/>
-      <c r="E10" s="176"/>
-      <c r="F10" s="176"/>
-      <c r="G10" s="176"/>
-      <c r="H10" s="176"/>
-      <c r="I10" s="176"/>
-      <c r="J10" s="176"/>
-      <c r="K10" s="176"/>
-      <c r="L10" s="179"/>
+      <c r="A10" s="153"/>
+      <c r="B10" s="154"/>
+      <c r="C10" s="154"/>
+      <c r="D10" s="154"/>
+      <c r="E10" s="154"/>
+      <c r="F10" s="154"/>
+      <c r="G10" s="154"/>
+      <c r="H10" s="154"/>
+      <c r="I10" s="154"/>
+      <c r="J10" s="154"/>
+      <c r="K10" s="154"/>
+      <c r="L10" s="155"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="201"/>
-      <c r="B11" s="176"/>
-      <c r="C11" s="176"/>
-      <c r="D11" s="176"/>
-      <c r="E11" s="176"/>
-      <c r="F11" s="176"/>
-      <c r="G11" s="176"/>
-      <c r="H11" s="176"/>
-      <c r="I11" s="176"/>
-      <c r="J11" s="176"/>
-      <c r="K11" s="176"/>
-      <c r="L11" s="179"/>
+      <c r="A11" s="153"/>
+      <c r="B11" s="154"/>
+      <c r="C11" s="154"/>
+      <c r="D11" s="154"/>
+      <c r="E11" s="154"/>
+      <c r="F11" s="154"/>
+      <c r="G11" s="154"/>
+      <c r="H11" s="154"/>
+      <c r="I11" s="154"/>
+      <c r="J11" s="154"/>
+      <c r="K11" s="154"/>
+      <c r="L11" s="155"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="202" t="s">
+      <c r="A12" s="156" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="203"/>
-      <c r="C12" s="203"/>
-      <c r="D12" s="203"/>
-      <c r="E12" s="203"/>
-      <c r="F12" s="203"/>
-      <c r="G12" s="203"/>
-      <c r="H12" s="203"/>
-      <c r="I12" s="203"/>
-      <c r="J12" s="203"/>
-      <c r="K12" s="203"/>
-      <c r="L12" s="204"/>
+      <c r="B12" s="157"/>
+      <c r="C12" s="157"/>
+      <c r="D12" s="157"/>
+      <c r="E12" s="157"/>
+      <c r="F12" s="157"/>
+      <c r="G12" s="157"/>
+      <c r="H12" s="157"/>
+      <c r="I12" s="157"/>
+      <c r="J12" s="157"/>
+      <c r="K12" s="157"/>
+      <c r="L12" s="158"/>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="205"/>
-      <c r="B13" s="206"/>
-      <c r="C13" s="206"/>
-      <c r="D13" s="206"/>
-      <c r="E13" s="206"/>
-      <c r="F13" s="206"/>
-      <c r="G13" s="206"/>
-      <c r="H13" s="206"/>
-      <c r="I13" s="206"/>
-      <c r="J13" s="206"/>
-      <c r="K13" s="206"/>
-      <c r="L13" s="207"/>
+      <c r="A13" s="159"/>
+      <c r="B13" s="160"/>
+      <c r="C13" s="160"/>
+      <c r="D13" s="160"/>
+      <c r="E13" s="160"/>
+      <c r="F13" s="160"/>
+      <c r="G13" s="160"/>
+      <c r="H13" s="160"/>
+      <c r="I13" s="160"/>
+      <c r="J13" s="160"/>
+      <c r="K13" s="160"/>
+      <c r="L13" s="161"/>
     </row>
     <row r="14" spans="1:20" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="208" t="s">
+      <c r="A14" s="162" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="209"/>
-      <c r="C14" s="212" t="s">
+      <c r="B14" s="163"/>
+      <c r="C14" s="166" t="s">
         <v>153</v>
       </c>
-      <c r="D14" s="212"/>
-      <c r="E14" s="212"/>
-      <c r="F14" s="217" t="s">
+      <c r="D14" s="166"/>
+      <c r="E14" s="166"/>
+      <c r="F14" s="169" t="s">
         <v>0</v>
       </c>
-      <c r="G14" s="218"/>
-      <c r="H14" s="218"/>
-      <c r="I14" s="218"/>
-      <c r="J14" s="219"/>
-      <c r="K14" s="223" t="s">
+      <c r="G14" s="170"/>
+      <c r="H14" s="170"/>
+      <c r="I14" s="170"/>
+      <c r="J14" s="171"/>
+      <c r="K14" s="175" t="s">
         <v>154</v>
       </c>
-      <c r="L14" s="224"/>
+      <c r="L14" s="176"/>
     </row>
     <row r="15" spans="1:20" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="210"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="212"/>
-      <c r="D15" s="212"/>
-      <c r="E15" s="212"/>
-      <c r="F15" s="220"/>
-      <c r="G15" s="221"/>
-      <c r="H15" s="221"/>
-      <c r="I15" s="221"/>
-      <c r="J15" s="222"/>
-      <c r="K15" s="225"/>
-      <c r="L15" s="226"/>
+      <c r="A15" s="164"/>
+      <c r="B15" s="165"/>
+      <c r="C15" s="166"/>
+      <c r="D15" s="166"/>
+      <c r="E15" s="166"/>
+      <c r="F15" s="172"/>
+      <c r="G15" s="173"/>
+      <c r="H15" s="173"/>
+      <c r="I15" s="173"/>
+      <c r="J15" s="174"/>
+      <c r="K15" s="177"/>
+      <c r="L15" s="178"/>
       <c r="T15" s="4"/>
     </row>
     <row r="16" spans="1:20" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="227" t="s">
+      <c r="A16" s="179" t="s">
         <v>71</v>
       </c>
-      <c r="B16" s="228"/>
-      <c r="C16" s="213" t="s">
+      <c r="B16" s="180"/>
+      <c r="C16" s="138" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="213"/>
-      <c r="E16" s="213"/>
-      <c r="F16" s="213" t="s">
+      <c r="D16" s="138"/>
+      <c r="E16" s="138"/>
+      <c r="F16" s="138" t="s">
         <v>70</v>
       </c>
-      <c r="G16" s="213"/>
-      <c r="H16" s="213"/>
-      <c r="I16" s="234" t="s">
+      <c r="G16" s="138"/>
+      <c r="H16" s="138"/>
+      <c r="I16" s="142" t="s">
         <v>3</v>
       </c>
-      <c r="J16" s="234"/>
-      <c r="K16" s="213" t="s">
+      <c r="J16" s="142"/>
+      <c r="K16" s="138" t="s">
         <v>5</v>
       </c>
-      <c r="L16" s="214"/>
+      <c r="L16" s="167"/>
     </row>
     <row r="17" spans="1:20" ht="22.9" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="215" t="s">
+      <c r="A17" s="168" t="s">
         <v>68</v>
       </c>
-      <c r="B17" s="216"/>
-      <c r="C17" s="229"/>
-      <c r="D17" s="229"/>
-      <c r="E17" s="229"/>
-      <c r="F17" s="232"/>
-      <c r="G17" s="216"/>
-      <c r="H17" s="233"/>
-      <c r="I17" s="235"/>
-      <c r="J17" s="235"/>
-      <c r="K17" s="230"/>
-      <c r="L17" s="231"/>
+      <c r="B17" s="140"/>
+      <c r="C17" s="181"/>
+      <c r="D17" s="181"/>
+      <c r="E17" s="181"/>
+      <c r="F17" s="139"/>
+      <c r="G17" s="140"/>
+      <c r="H17" s="141"/>
+      <c r="I17" s="143"/>
+      <c r="J17" s="143"/>
+      <c r="K17" s="136"/>
+      <c r="L17" s="137"/>
     </row>
     <row r="18" spans="1:20" ht="23.45" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="215" t="s">
+      <c r="A18" s="168" t="s">
         <v>69</v>
       </c>
-      <c r="B18" s="216"/>
-      <c r="C18" s="229"/>
-      <c r="D18" s="229"/>
-      <c r="E18" s="229"/>
-      <c r="F18" s="232"/>
-      <c r="G18" s="216"/>
-      <c r="H18" s="233"/>
-      <c r="I18" s="236"/>
-      <c r="J18" s="237"/>
+      <c r="B18" s="140"/>
+      <c r="C18" s="181"/>
+      <c r="D18" s="181"/>
+      <c r="E18" s="181"/>
+      <c r="F18" s="139"/>
+      <c r="G18" s="140"/>
+      <c r="H18" s="141"/>
+      <c r="I18" s="144"/>
+      <c r="J18" s="145"/>
       <c r="K18" s="45"/>
       <c r="L18" s="60"/>
       <c r="T18" s="4"/>
@@ -4370,278 +4370,278 @@
       <c r="B19" s="107" t="s">
         <v>2</v>
       </c>
-      <c r="C19" s="155" t="s">
+      <c r="C19" s="182" t="s">
         <v>3</v>
       </c>
-      <c r="D19" s="155"/>
-      <c r="E19" s="196"/>
-      <c r="F19" s="194" t="s">
+      <c r="D19" s="182"/>
+      <c r="E19" s="148"/>
+      <c r="F19" s="146" t="s">
         <v>4</v>
       </c>
-      <c r="G19" s="195"/>
-      <c r="H19" s="195"/>
-      <c r="I19" s="195"/>
-      <c r="J19" s="195"/>
-      <c r="K19" s="196" t="s">
+      <c r="G19" s="147"/>
+      <c r="H19" s="147"/>
+      <c r="I19" s="147"/>
+      <c r="J19" s="147"/>
+      <c r="K19" s="148" t="s">
         <v>5</v>
       </c>
-      <c r="L19" s="197"/>
+      <c r="L19" s="149"/>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="99">
         <v>0</v>
       </c>
       <c r="B20" s="100"/>
-      <c r="C20" s="189" t="s">
+      <c r="C20" s="183" t="s">
         <v>151</v>
       </c>
-      <c r="D20" s="189"/>
-      <c r="E20" s="189"/>
-      <c r="F20" s="190" t="s">
+      <c r="D20" s="183"/>
+      <c r="E20" s="183"/>
+      <c r="F20" s="184" t="s">
         <v>155</v>
       </c>
-      <c r="G20" s="191"/>
-      <c r="H20" s="191"/>
-      <c r="I20" s="191"/>
-      <c r="J20" s="191"/>
-      <c r="K20" s="192">
+      <c r="G20" s="185"/>
+      <c r="H20" s="185"/>
+      <c r="I20" s="185"/>
+      <c r="J20" s="185"/>
+      <c r="K20" s="186">
         <v>46187</v>
       </c>
-      <c r="L20" s="193"/>
+      <c r="L20" s="187"/>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="61">
         <v>2</v>
       </c>
       <c r="B21" s="12"/>
-      <c r="C21" s="184"/>
-      <c r="D21" s="184"/>
-      <c r="E21" s="184"/>
-      <c r="F21" s="185"/>
-      <c r="G21" s="186"/>
-      <c r="H21" s="186"/>
-      <c r="I21" s="186"/>
-      <c r="J21" s="186"/>
-      <c r="K21" s="187"/>
-      <c r="L21" s="188"/>
+      <c r="C21" s="191"/>
+      <c r="D21" s="191"/>
+      <c r="E21" s="191"/>
+      <c r="F21" s="192"/>
+      <c r="G21" s="193"/>
+      <c r="H21" s="193"/>
+      <c r="I21" s="193"/>
+      <c r="J21" s="193"/>
+      <c r="K21" s="194"/>
+      <c r="L21" s="195"/>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="62">
         <v>3</v>
       </c>
       <c r="B22" s="54"/>
-      <c r="C22" s="171"/>
-      <c r="D22" s="171"/>
-      <c r="E22" s="171"/>
-      <c r="F22" s="172"/>
-      <c r="G22" s="173"/>
-      <c r="H22" s="173"/>
-      <c r="I22" s="173"/>
-      <c r="J22" s="173"/>
-      <c r="K22" s="182"/>
-      <c r="L22" s="183"/>
+      <c r="C22" s="188"/>
+      <c r="D22" s="188"/>
+      <c r="E22" s="188"/>
+      <c r="F22" s="196"/>
+      <c r="G22" s="197"/>
+      <c r="H22" s="197"/>
+      <c r="I22" s="197"/>
+      <c r="J22" s="197"/>
+      <c r="K22" s="189"/>
+      <c r="L22" s="190"/>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="62">
         <v>4</v>
       </c>
       <c r="B23" s="54"/>
-      <c r="C23" s="171"/>
-      <c r="D23" s="171"/>
-      <c r="E23" s="171"/>
-      <c r="F23" s="172"/>
-      <c r="G23" s="173"/>
-      <c r="H23" s="173"/>
-      <c r="I23" s="173"/>
-      <c r="J23" s="173"/>
-      <c r="K23" s="182"/>
-      <c r="L23" s="183"/>
+      <c r="C23" s="188"/>
+      <c r="D23" s="188"/>
+      <c r="E23" s="188"/>
+      <c r="F23" s="196"/>
+      <c r="G23" s="197"/>
+      <c r="H23" s="197"/>
+      <c r="I23" s="197"/>
+      <c r="J23" s="197"/>
+      <c r="K23" s="189"/>
+      <c r="L23" s="190"/>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="62">
         <v>5</v>
       </c>
       <c r="B24" s="54"/>
-      <c r="C24" s="171"/>
-      <c r="D24" s="171"/>
-      <c r="E24" s="171"/>
-      <c r="F24" s="172"/>
-      <c r="G24" s="173"/>
-      <c r="H24" s="173"/>
-      <c r="I24" s="173"/>
-      <c r="J24" s="173"/>
-      <c r="K24" s="182"/>
-      <c r="L24" s="183"/>
+      <c r="C24" s="188"/>
+      <c r="D24" s="188"/>
+      <c r="E24" s="188"/>
+      <c r="F24" s="196"/>
+      <c r="G24" s="197"/>
+      <c r="H24" s="197"/>
+      <c r="I24" s="197"/>
+      <c r="J24" s="197"/>
+      <c r="K24" s="189"/>
+      <c r="L24" s="190"/>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="62"/>
       <c r="B25" s="54"/>
-      <c r="C25" s="171"/>
-      <c r="D25" s="171"/>
-      <c r="E25" s="171"/>
-      <c r="F25" s="180"/>
-      <c r="G25" s="181"/>
-      <c r="H25" s="181"/>
-      <c r="I25" s="181"/>
-      <c r="J25" s="181"/>
-      <c r="K25" s="182"/>
-      <c r="L25" s="183"/>
+      <c r="C25" s="188"/>
+      <c r="D25" s="188"/>
+      <c r="E25" s="188"/>
+      <c r="F25" s="198"/>
+      <c r="G25" s="199"/>
+      <c r="H25" s="199"/>
+      <c r="I25" s="199"/>
+      <c r="J25" s="199"/>
+      <c r="K25" s="189"/>
+      <c r="L25" s="190"/>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="62"/>
       <c r="B26" s="54"/>
-      <c r="C26" s="171"/>
-      <c r="D26" s="171"/>
-      <c r="E26" s="171"/>
-      <c r="F26" s="172"/>
-      <c r="G26" s="173"/>
-      <c r="H26" s="173"/>
-      <c r="I26" s="173"/>
-      <c r="J26" s="173"/>
-      <c r="K26" s="182"/>
-      <c r="L26" s="183"/>
+      <c r="C26" s="188"/>
+      <c r="D26" s="188"/>
+      <c r="E26" s="188"/>
+      <c r="F26" s="196"/>
+      <c r="G26" s="197"/>
+      <c r="H26" s="197"/>
+      <c r="I26" s="197"/>
+      <c r="J26" s="197"/>
+      <c r="K26" s="189"/>
+      <c r="L26" s="190"/>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="62"/>
       <c r="B27" s="54"/>
-      <c r="C27" s="171"/>
-      <c r="D27" s="171"/>
-      <c r="E27" s="171"/>
-      <c r="F27" s="180"/>
-      <c r="G27" s="181"/>
-      <c r="H27" s="181"/>
-      <c r="I27" s="181"/>
-      <c r="J27" s="181"/>
-      <c r="K27" s="182"/>
-      <c r="L27" s="183"/>
+      <c r="C27" s="188"/>
+      <c r="D27" s="188"/>
+      <c r="E27" s="188"/>
+      <c r="F27" s="198"/>
+      <c r="G27" s="199"/>
+      <c r="H27" s="199"/>
+      <c r="I27" s="199"/>
+      <c r="J27" s="199"/>
+      <c r="K27" s="189"/>
+      <c r="L27" s="190"/>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="62"/>
       <c r="B28" s="54"/>
-      <c r="C28" s="171"/>
-      <c r="D28" s="171"/>
-      <c r="E28" s="171"/>
-      <c r="F28" s="172"/>
-      <c r="G28" s="181"/>
-      <c r="H28" s="181"/>
-      <c r="I28" s="181"/>
-      <c r="J28" s="181"/>
-      <c r="K28" s="182"/>
-      <c r="L28" s="183"/>
+      <c r="C28" s="188"/>
+      <c r="D28" s="188"/>
+      <c r="E28" s="188"/>
+      <c r="F28" s="196"/>
+      <c r="G28" s="199"/>
+      <c r="H28" s="199"/>
+      <c r="I28" s="199"/>
+      <c r="J28" s="199"/>
+      <c r="K28" s="189"/>
+      <c r="L28" s="190"/>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="62"/>
       <c r="B29" s="54"/>
-      <c r="C29" s="171"/>
-      <c r="D29" s="171"/>
-      <c r="E29" s="171"/>
-      <c r="F29" s="172"/>
-      <c r="G29" s="173"/>
-      <c r="H29" s="173"/>
-      <c r="I29" s="173"/>
-      <c r="J29" s="173"/>
-      <c r="K29" s="174"/>
-      <c r="L29" s="175"/>
+      <c r="C29" s="188"/>
+      <c r="D29" s="188"/>
+      <c r="E29" s="188"/>
+      <c r="F29" s="196"/>
+      <c r="G29" s="197"/>
+      <c r="H29" s="197"/>
+      <c r="I29" s="197"/>
+      <c r="J29" s="197"/>
+      <c r="K29" s="200"/>
+      <c r="L29" s="201"/>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="63"/>
       <c r="B30" s="53"/>
-      <c r="C30" s="176"/>
-      <c r="D30" s="176"/>
-      <c r="E30" s="176"/>
-      <c r="F30" s="177"/>
-      <c r="G30" s="178"/>
-      <c r="H30" s="178"/>
-      <c r="I30" s="178"/>
-      <c r="J30" s="178"/>
-      <c r="K30" s="176"/>
-      <c r="L30" s="179"/>
+      <c r="C30" s="154"/>
+      <c r="D30" s="154"/>
+      <c r="E30" s="154"/>
+      <c r="F30" s="202"/>
+      <c r="G30" s="203"/>
+      <c r="H30" s="203"/>
+      <c r="I30" s="203"/>
+      <c r="J30" s="203"/>
+      <c r="K30" s="154"/>
+      <c r="L30" s="155"/>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="58"/>
       <c r="B31" s="10"/>
-      <c r="C31" s="150"/>
-      <c r="D31" s="150"/>
-      <c r="E31" s="150"/>
-      <c r="F31" s="159"/>
-      <c r="G31" s="160"/>
-      <c r="H31" s="160"/>
-      <c r="I31" s="160"/>
-      <c r="J31" s="160"/>
-      <c r="K31" s="150"/>
-      <c r="L31" s="147"/>
+      <c r="C31" s="204"/>
+      <c r="D31" s="204"/>
+      <c r="E31" s="204"/>
+      <c r="F31" s="205"/>
+      <c r="G31" s="206"/>
+      <c r="H31" s="206"/>
+      <c r="I31" s="206"/>
+      <c r="J31" s="206"/>
+      <c r="K31" s="204"/>
+      <c r="L31" s="207"/>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="58"/>
       <c r="B32" s="10"/>
-      <c r="C32" s="150"/>
-      <c r="D32" s="150"/>
-      <c r="E32" s="150"/>
-      <c r="F32" s="159"/>
-      <c r="G32" s="160"/>
-      <c r="H32" s="160"/>
-      <c r="I32" s="160"/>
-      <c r="J32" s="160"/>
-      <c r="K32" s="150"/>
-      <c r="L32" s="147"/>
+      <c r="C32" s="204"/>
+      <c r="D32" s="204"/>
+      <c r="E32" s="204"/>
+      <c r="F32" s="205"/>
+      <c r="G32" s="206"/>
+      <c r="H32" s="206"/>
+      <c r="I32" s="206"/>
+      <c r="J32" s="206"/>
+      <c r="K32" s="204"/>
+      <c r="L32" s="207"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="58"/>
       <c r="B33" s="10"/>
-      <c r="C33" s="150"/>
-      <c r="D33" s="150"/>
-      <c r="E33" s="150"/>
-      <c r="F33" s="159"/>
-      <c r="G33" s="160"/>
-      <c r="H33" s="160"/>
-      <c r="I33" s="160"/>
-      <c r="J33" s="160"/>
-      <c r="K33" s="150"/>
-      <c r="L33" s="147"/>
+      <c r="C33" s="204"/>
+      <c r="D33" s="204"/>
+      <c r="E33" s="204"/>
+      <c r="F33" s="205"/>
+      <c r="G33" s="206"/>
+      <c r="H33" s="206"/>
+      <c r="I33" s="206"/>
+      <c r="J33" s="206"/>
+      <c r="K33" s="204"/>
+      <c r="L33" s="207"/>
     </row>
     <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="59"/>
       <c r="B34" s="19"/>
-      <c r="C34" s="148"/>
-      <c r="D34" s="148"/>
-      <c r="E34" s="148"/>
-      <c r="F34" s="169"/>
-      <c r="G34" s="170"/>
-      <c r="H34" s="170"/>
-      <c r="I34" s="170"/>
-      <c r="J34" s="170"/>
-      <c r="K34" s="148"/>
-      <c r="L34" s="149"/>
+      <c r="C34" s="222"/>
+      <c r="D34" s="222"/>
+      <c r="E34" s="222"/>
+      <c r="F34" s="223"/>
+      <c r="G34" s="224"/>
+      <c r="H34" s="224"/>
+      <c r="I34" s="224"/>
+      <c r="J34" s="224"/>
+      <c r="K34" s="222"/>
+      <c r="L34" s="225"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="161" t="s">
+      <c r="A35" s="213" t="s">
         <v>14</v>
       </c>
-      <c r="B35" s="162"/>
-      <c r="C35" s="163"/>
-      <c r="D35" s="163"/>
-      <c r="E35" s="163"/>
-      <c r="F35" s="163"/>
-      <c r="G35" s="163"/>
-      <c r="H35" s="163"/>
-      <c r="I35" s="163"/>
-      <c r="J35" s="163"/>
-      <c r="K35" s="163"/>
-      <c r="L35" s="164"/>
+      <c r="B35" s="214"/>
+      <c r="C35" s="215"/>
+      <c r="D35" s="215"/>
+      <c r="E35" s="215"/>
+      <c r="F35" s="215"/>
+      <c r="G35" s="215"/>
+      <c r="H35" s="215"/>
+      <c r="I35" s="215"/>
+      <c r="J35" s="215"/>
+      <c r="K35" s="215"/>
+      <c r="L35" s="216"/>
     </row>
     <row r="36" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="165"/>
-      <c r="B36" s="166"/>
-      <c r="C36" s="166"/>
-      <c r="D36" s="166"/>
-      <c r="E36" s="166"/>
-      <c r="F36" s="166"/>
-      <c r="G36" s="166"/>
-      <c r="H36" s="166"/>
-      <c r="I36" s="166"/>
-      <c r="J36" s="166"/>
-      <c r="K36" s="166"/>
-      <c r="L36" s="167"/>
+      <c r="A36" s="217"/>
+      <c r="B36" s="218"/>
+      <c r="C36" s="218"/>
+      <c r="D36" s="218"/>
+      <c r="E36" s="218"/>
+      <c r="F36" s="218"/>
+      <c r="G36" s="218"/>
+      <c r="H36" s="218"/>
+      <c r="I36" s="218"/>
+      <c r="J36" s="218"/>
+      <c r="K36" s="218"/>
+      <c r="L36" s="219"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="106" t="s">
@@ -4659,19 +4659,19 @@
       <c r="E37" s="107" t="s">
         <v>78</v>
       </c>
-      <c r="F37" s="156" t="s">
+      <c r="F37" s="210" t="s">
         <v>44</v>
       </c>
-      <c r="G37" s="157"/>
-      <c r="H37" s="158"/>
-      <c r="I37" s="155" t="s">
+      <c r="G37" s="211"/>
+      <c r="H37" s="212"/>
+      <c r="I37" s="182" t="s">
         <v>19</v>
       </c>
-      <c r="J37" s="155"/>
-      <c r="K37" s="155" t="s">
+      <c r="J37" s="182"/>
+      <c r="K37" s="182" t="s">
         <v>5</v>
       </c>
-      <c r="L37" s="168"/>
+      <c r="L37" s="220"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="58">
@@ -4681,13 +4681,13 @@
       <c r="C38" s="10"/>
       <c r="D38" s="10"/>
       <c r="E38" s="10"/>
-      <c r="F38" s="150"/>
-      <c r="G38" s="150"/>
-      <c r="H38" s="150"/>
-      <c r="I38" s="151"/>
-      <c r="J38" s="152"/>
-      <c r="K38" s="146"/>
-      <c r="L38" s="147"/>
+      <c r="F38" s="204"/>
+      <c r="G38" s="204"/>
+      <c r="H38" s="204"/>
+      <c r="I38" s="208"/>
+      <c r="J38" s="209"/>
+      <c r="K38" s="221"/>
+      <c r="L38" s="207"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="58">
@@ -4697,13 +4697,13 @@
       <c r="C39" s="10"/>
       <c r="D39" s="10"/>
       <c r="E39" s="10"/>
-      <c r="F39" s="150"/>
-      <c r="G39" s="150"/>
-      <c r="H39" s="150"/>
-      <c r="I39" s="151"/>
-      <c r="J39" s="152"/>
-      <c r="K39" s="146"/>
-      <c r="L39" s="147"/>
+      <c r="F39" s="204"/>
+      <c r="G39" s="204"/>
+      <c r="H39" s="204"/>
+      <c r="I39" s="208"/>
+      <c r="J39" s="209"/>
+      <c r="K39" s="221"/>
+      <c r="L39" s="207"/>
     </row>
     <row r="40" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="59"/>
@@ -4711,26 +4711,77 @@
       <c r="C40" s="14"/>
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
-      <c r="F40" s="148"/>
-      <c r="G40" s="148"/>
-      <c r="H40" s="148"/>
-      <c r="I40" s="153"/>
-      <c r="J40" s="154"/>
-      <c r="K40" s="148"/>
-      <c r="L40" s="149"/>
+      <c r="F40" s="222"/>
+      <c r="G40" s="222"/>
+      <c r="H40" s="222"/>
+      <c r="I40" s="226"/>
+      <c r="J40" s="227"/>
+      <c r="K40" s="222"/>
+      <c r="L40" s="225"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B42" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="81">
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="F33:J33"/>
+    <mergeCell ref="A35:L36"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F34:J34"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="F31:J31"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="F32:J32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="F29:J29"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="F30:J30"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="F27:J27"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="F28:J28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="F25:J25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="F26:J26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="F21:J21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="F22:J22"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="F23:J23"/>
+    <mergeCell ref="F24:J24"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="F20:J20"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="K23:L23"/>
     <mergeCell ref="F19:J19"/>
     <mergeCell ref="K19:L19"/>
     <mergeCell ref="A1:L11"/>
@@ -4747,64 +4798,13 @@
     <mergeCell ref="C17:E17"/>
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="F20:J20"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="F21:J21"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="F22:J22"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="F23:J23"/>
-    <mergeCell ref="F24:J24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="F25:J25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="F26:J26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="F27:J27"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="F28:J28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="F29:J29"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="F30:J30"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="F31:J31"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="F32:J32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="F33:J33"/>
-    <mergeCell ref="A35:L36"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="F34:J34"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="I18:J18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4829,52 +4829,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="244" t="s">
+      <c r="A1" s="127" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="245"/>
-      <c r="C1" s="250" t="s">
+      <c r="B1" s="128"/>
+      <c r="C1" s="133" t="s">
         <v>93</v>
       </c>
-      <c r="D1" s="251"/>
-      <c r="E1" s="251"/>
-      <c r="F1" s="251"/>
-      <c r="G1" s="251"/>
-      <c r="H1" s="251"/>
-      <c r="I1" s="251"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
     </row>
     <row r="2" spans="1:32" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="246"/>
-      <c r="B2" s="247"/>
-      <c r="C2" s="123" t="s">
+      <c r="A2" s="129"/>
+      <c r="B2" s="130"/>
+      <c r="C2" s="135" t="s">
         <v>117</v>
       </c>
-      <c r="D2" s="123" t="s">
+      <c r="D2" s="135" t="s">
+        <v>201</v>
+      </c>
+      <c r="E2" s="135" t="s">
+        <v>202</v>
+      </c>
+      <c r="F2" s="135" t="s">
         <v>203</v>
       </c>
-      <c r="E2" s="123" t="s">
-        <v>201</v>
-      </c>
-      <c r="F2" s="123" t="s">
-        <v>202</v>
-      </c>
-      <c r="G2" s="123"/>
-      <c r="H2" s="123"/>
-      <c r="I2" s="123"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
     </row>
     <row r="3" spans="1:32" ht="147.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="248"/>
-      <c r="B3" s="249"/>
-      <c r="C3" s="123"/>
-      <c r="D3" s="123"/>
-      <c r="E3" s="123"/>
-      <c r="F3" s="123"/>
-      <c r="G3" s="123"/>
-      <c r="H3" s="123"/>
-      <c r="I3" s="123"/>
+      <c r="A3" s="131"/>
+      <c r="B3" s="132"/>
+      <c r="C3" s="135"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="135"/>
+      <c r="I3" s="135"/>
     </row>
     <row r="4" spans="1:32" ht="55.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="238" t="s">
+      <c r="A4" s="121" t="s">
         <v>92</v>
       </c>
       <c r="B4" s="105" t="s">
@@ -4894,7 +4894,7 @@
       </c>
     </row>
     <row r="5" spans="1:32" ht="55.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="239"/>
+      <c r="A5" s="122"/>
       <c r="B5" s="105" t="s">
         <v>120</v>
       </c>
@@ -4911,7 +4911,7 @@
       <c r="I5" s="85"/>
     </row>
     <row r="6" spans="1:32" ht="55.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="239"/>
+      <c r="A6" s="122"/>
       <c r="B6" s="105"/>
       <c r="C6" s="86"/>
       <c r="D6" s="83"/>
@@ -4922,7 +4922,7 @@
       <c r="I6" s="85"/>
     </row>
     <row r="7" spans="1:32" ht="55.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="239"/>
+      <c r="A7" s="122"/>
       <c r="B7" s="105"/>
       <c r="C7" s="86"/>
       <c r="D7" s="83"/>
@@ -4933,7 +4933,7 @@
       <c r="I7" s="85"/>
     </row>
     <row r="8" spans="1:32" ht="55.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="239"/>
+      <c r="A8" s="122"/>
       <c r="B8" s="105"/>
       <c r="C8" s="86"/>
       <c r="D8" s="83"/>
@@ -4944,7 +4944,7 @@
       <c r="I8" s="87"/>
     </row>
     <row r="9" spans="1:32" ht="55.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="239"/>
+      <c r="A9" s="122"/>
       <c r="B9" s="105"/>
       <c r="C9" s="79"/>
       <c r="D9" s="88"/>
@@ -4955,7 +4955,7 @@
       <c r="I9" s="91"/>
     </row>
     <row r="10" spans="1:32" ht="55.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="239"/>
+      <c r="A10" s="122"/>
       <c r="B10" s="105"/>
       <c r="C10" s="89"/>
       <c r="D10" s="89"/>
@@ -4966,7 +4966,7 @@
       <c r="I10" s="91"/>
     </row>
     <row r="11" spans="1:32" ht="55.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="239"/>
+      <c r="A11" s="122"/>
       <c r="B11" s="105"/>
       <c r="C11" s="89"/>
       <c r="D11" s="89"/>
@@ -4977,7 +4977,7 @@
       <c r="I11" s="91"/>
     </row>
     <row r="12" spans="1:32" ht="55.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="240"/>
+      <c r="A12" s="123"/>
       <c r="B12" s="105"/>
       <c r="C12" s="93"/>
       <c r="D12" s="93"/>
@@ -4989,17 +4989,17 @@
     </row>
     <row r="14" spans="1:32" ht="32.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="1:32" ht="32.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="241" t="s">
+      <c r="A15" s="124" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="242"/>
-      <c r="C15" s="242"/>
-      <c r="D15" s="242"/>
-      <c r="E15" s="242"/>
-      <c r="F15" s="242"/>
-      <c r="G15" s="242"/>
-      <c r="H15" s="242"/>
-      <c r="I15" s="243"/>
+      <c r="B15" s="125"/>
+      <c r="C15" s="125"/>
+      <c r="D15" s="125"/>
+      <c r="E15" s="125"/>
+      <c r="F15" s="125"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="125"/>
+      <c r="I15" s="126"/>
       <c r="J15" s="96"/>
     </row>
     <row r="16" spans="1:32" ht="32.1" customHeight="1" x14ac:dyDescent="0.5">
@@ -5358,122 +5358,122 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="237" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="137"/>
-      <c r="E1" s="131" t="s">
+      <c r="B1" s="237"/>
+      <c r="C1" s="237"/>
+      <c r="D1" s="238"/>
+      <c r="E1" s="232" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
-      <c r="J1" s="132"/>
-      <c r="K1" s="132"/>
-      <c r="L1" s="132"/>
-      <c r="M1" s="132"/>
-      <c r="N1" s="132"/>
-      <c r="O1" s="132"/>
-      <c r="P1" s="132"/>
-      <c r="Q1" s="132"/>
-      <c r="R1" s="133"/>
-      <c r="S1" s="121" t="s">
+      <c r="F1" s="233"/>
+      <c r="G1" s="233"/>
+      <c r="H1" s="233"/>
+      <c r="I1" s="233"/>
+      <c r="J1" s="233"/>
+      <c r="K1" s="233"/>
+      <c r="L1" s="233"/>
+      <c r="M1" s="233"/>
+      <c r="N1" s="233"/>
+      <c r="O1" s="233"/>
+      <c r="P1" s="233"/>
+      <c r="Q1" s="233"/>
+      <c r="R1" s="234"/>
+      <c r="S1" s="247" t="s">
         <v>25</v>
       </c>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
+      <c r="T1" s="248"/>
+      <c r="U1" s="248"/>
+      <c r="V1" s="248"/>
     </row>
     <row r="2" spans="1:22" s="2" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="127" t="s">
+      <c r="A2" s="228" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="127"/>
-      <c r="C2" s="138" t="s">
+      <c r="B2" s="228"/>
+      <c r="C2" s="239" t="s">
         <v>116</v>
       </c>
-      <c r="D2" s="139"/>
-      <c r="E2" s="144" t="s">
+      <c r="D2" s="240"/>
+      <c r="E2" s="245" t="s">
         <v>80</v>
       </c>
-      <c r="F2" s="123" t="s">
+      <c r="F2" s="135" t="s">
         <v>87</v>
       </c>
-      <c r="G2" s="123" t="s">
+      <c r="G2" s="135" t="s">
         <v>81</v>
       </c>
-      <c r="H2" s="123" t="s">
+      <c r="H2" s="135" t="s">
         <v>82</v>
       </c>
-      <c r="I2" s="123" t="s">
+      <c r="I2" s="135" t="s">
         <v>83</v>
       </c>
-      <c r="J2" s="123" t="s">
+      <c r="J2" s="135" t="s">
         <v>84</v>
       </c>
-      <c r="K2" s="123" t="s">
+      <c r="K2" s="135" t="s">
         <v>85</v>
       </c>
-      <c r="L2" s="123" t="s">
+      <c r="L2" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="M2" s="129" t="s">
+      <c r="M2" s="230" t="s">
         <v>111</v>
       </c>
-      <c r="N2" s="129" t="s">
+      <c r="N2" s="230" t="s">
         <v>76</v>
       </c>
-      <c r="O2" s="142" t="s">
+      <c r="O2" s="243" t="s">
         <v>34</v>
       </c>
-      <c r="P2" s="142" t="s">
+      <c r="P2" s="243" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="142" t="s">
+      <c r="Q2" s="243" t="s">
         <v>15</v>
       </c>
-      <c r="R2" s="134" t="s">
+      <c r="R2" s="235" t="s">
         <v>17</v>
       </c>
-      <c r="S2" s="124" t="s">
+      <c r="S2" s="249" t="s">
         <v>6</v>
       </c>
-      <c r="T2" s="124" t="s">
+      <c r="T2" s="249" t="s">
         <v>152</v>
       </c>
-      <c r="U2" s="124" t="s">
+      <c r="U2" s="249" t="s">
         <v>199</v>
       </c>
-      <c r="V2" s="124" t="s">
+      <c r="V2" s="249" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:22" s="2" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="128"/>
-      <c r="B3" s="128"/>
-      <c r="C3" s="140"/>
-      <c r="D3" s="141"/>
-      <c r="E3" s="144"/>
-      <c r="F3" s="145"/>
-      <c r="G3" s="123"/>
-      <c r="H3" s="123"/>
-      <c r="I3" s="123"/>
-      <c r="J3" s="123"/>
-      <c r="K3" s="123"/>
-      <c r="L3" s="123"/>
-      <c r="M3" s="130"/>
-      <c r="N3" s="130"/>
-      <c r="O3" s="143"/>
-      <c r="P3" s="143"/>
-      <c r="Q3" s="143"/>
-      <c r="R3" s="135"/>
-      <c r="S3" s="125"/>
-      <c r="T3" s="125"/>
-      <c r="U3" s="125"/>
-      <c r="V3" s="125"/>
+      <c r="A3" s="229"/>
+      <c r="B3" s="229"/>
+      <c r="C3" s="241"/>
+      <c r="D3" s="242"/>
+      <c r="E3" s="245"/>
+      <c r="F3" s="246"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="135"/>
+      <c r="I3" s="135"/>
+      <c r="J3" s="135"/>
+      <c r="K3" s="135"/>
+      <c r="L3" s="135"/>
+      <c r="M3" s="231"/>
+      <c r="N3" s="231"/>
+      <c r="O3" s="244"/>
+      <c r="P3" s="244"/>
+      <c r="Q3" s="244"/>
+      <c r="R3" s="236"/>
+      <c r="S3" s="250"/>
+      <c r="T3" s="250"/>
+      <c r="U3" s="250"/>
+      <c r="V3" s="250"/>
     </row>
     <row r="4" spans="1:22" s="2" customFormat="1" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
@@ -5488,24 +5488,24 @@
       <c r="D4" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="144"/>
-      <c r="F4" s="145"/>
-      <c r="G4" s="123"/>
-      <c r="H4" s="123"/>
-      <c r="I4" s="123"/>
-      <c r="J4" s="123"/>
-      <c r="K4" s="123"/>
-      <c r="L4" s="123"/>
-      <c r="M4" s="130"/>
-      <c r="N4" s="130"/>
-      <c r="O4" s="143"/>
-      <c r="P4" s="143"/>
-      <c r="Q4" s="143"/>
-      <c r="R4" s="135"/>
-      <c r="S4" s="126"/>
-      <c r="T4" s="126"/>
-      <c r="U4" s="126"/>
-      <c r="V4" s="126"/>
+      <c r="E4" s="245"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="135"/>
+      <c r="H4" s="135"/>
+      <c r="I4" s="135"/>
+      <c r="J4" s="135"/>
+      <c r="K4" s="135"/>
+      <c r="L4" s="135"/>
+      <c r="M4" s="231"/>
+      <c r="N4" s="231"/>
+      <c r="O4" s="244"/>
+      <c r="P4" s="244"/>
+      <c r="Q4" s="244"/>
+      <c r="R4" s="236"/>
+      <c r="S4" s="251"/>
+      <c r="T4" s="251"/>
+      <c r="U4" s="251"/>
+      <c r="V4" s="251"/>
     </row>
     <row r="5" spans="1:22" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
@@ -6493,6 +6493,13 @@
   </sheetData>
   <autoFilter ref="E2:V24" xr:uid="{00000000-0001-0000-0400-000000000000}"/>
   <mergeCells count="23">
+    <mergeCell ref="S1:V1"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="L2:L4"/>
+    <mergeCell ref="S2:S4"/>
+    <mergeCell ref="V2:V4"/>
+    <mergeCell ref="T2:T4"/>
+    <mergeCell ref="U2:U4"/>
     <mergeCell ref="A2:B3"/>
     <mergeCell ref="M2:M4"/>
     <mergeCell ref="E1:R1"/>
@@ -6509,13 +6516,6 @@
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
-    <mergeCell ref="S1:V1"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="L2:L4"/>
-    <mergeCell ref="S2:S4"/>
-    <mergeCell ref="V2:V4"/>
-    <mergeCell ref="T2:T4"/>
-    <mergeCell ref="U2:U4"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="A1:A3 A5:A1048576">
@@ -8876,37 +8876,37 @@
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="278" t="s">
+      <c r="A2" s="259" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="281" t="s">
+      <c r="B2" s="267" t="s">
         <v>113</v>
       </c>
-      <c r="C2" s="282"/>
+      <c r="C2" s="268"/>
     </row>
     <row r="3" spans="1:4" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="279"/>
-      <c r="B3" s="283"/>
-      <c r="C3" s="284"/>
+      <c r="A3" s="260"/>
+      <c r="B3" s="269"/>
+      <c r="C3" s="270"/>
     </row>
     <row r="4" spans="1:4" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="280"/>
-      <c r="B4" s="285"/>
-      <c r="C4" s="286"/>
+      <c r="A4" s="261"/>
+      <c r="B4" s="271"/>
+      <c r="C4" s="272"/>
     </row>
     <row r="5" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="1:4" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="68" t="s">
         <v>110</v>
       </c>
-      <c r="B6" s="260" t="s">
+      <c r="B6" s="279" t="s">
         <v>112</v>
       </c>
-      <c r="C6" s="261"/>
+      <c r="C6" s="280"/>
     </row>
     <row r="7" spans="1:4" ht="34.9" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="287"/>
-      <c r="B7" s="258" t="s">
+      <c r="A7" s="273"/>
+      <c r="B7" s="264" t="s">
         <v>27</v>
       </c>
       <c r="C7" s="36" t="s">
@@ -8915,40 +8915,40 @@
       <c r="D7" s="69"/>
     </row>
     <row r="8" spans="1:4" ht="34.9" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="254"/>
-      <c r="B8" s="262"/>
+      <c r="A8" s="274"/>
+      <c r="B8" s="281"/>
       <c r="C8" s="37" t="s">
         <v>29</v>
       </c>
       <c r="D8" s="69"/>
     </row>
     <row r="9" spans="1:4" ht="34.9" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="254"/>
-      <c r="B9" s="262"/>
+      <c r="A9" s="274"/>
+      <c r="B9" s="281"/>
       <c r="C9" s="37" t="s">
         <v>52</v>
       </c>
       <c r="D9" s="69"/>
     </row>
     <row r="10" spans="1:4" ht="34.9" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="254"/>
-      <c r="B10" s="262"/>
+      <c r="A10" s="274"/>
+      <c r="B10" s="281"/>
       <c r="C10" s="37" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="69"/>
     </row>
     <row r="11" spans="1:4" ht="34.9" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="254"/>
-      <c r="B11" s="259"/>
+      <c r="A11" s="274"/>
+      <c r="B11" s="266"/>
       <c r="C11" s="38" t="s">
         <v>31</v>
       </c>
       <c r="D11" s="69"/>
     </row>
     <row r="12" spans="1:4" ht="34.9" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="254"/>
-      <c r="B12" s="263" t="s">
+      <c r="A12" s="274"/>
+      <c r="B12" s="282" t="s">
         <v>32</v>
       </c>
       <c r="C12" s="36" t="s">
@@ -8956,15 +8956,15 @@
       </c>
     </row>
     <row r="13" spans="1:4" ht="34.9" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="254"/>
-      <c r="B13" s="264"/>
+      <c r="A13" s="274"/>
+      <c r="B13" s="283"/>
       <c r="C13" s="39" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="34.9" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="254"/>
-      <c r="B14" s="265" t="s">
+      <c r="A14" s="274"/>
+      <c r="B14" s="284" t="s">
         <v>39</v>
       </c>
       <c r="C14" s="36" t="s">
@@ -8972,22 +8972,22 @@
       </c>
     </row>
     <row r="15" spans="1:4" ht="34.9" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="254"/>
-      <c r="B15" s="266"/>
+      <c r="A15" s="274"/>
+      <c r="B15" s="262"/>
       <c r="C15" s="37" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="34.9" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="254"/>
-      <c r="B16" s="266"/>
+      <c r="A16" s="274"/>
+      <c r="B16" s="262"/>
       <c r="C16" s="44" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="34.9" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="255"/>
-      <c r="B17" s="267"/>
+      <c r="A17" s="275"/>
+      <c r="B17" s="263"/>
       <c r="C17" s="39" t="s">
         <v>33</v>
       </c>
@@ -8997,14 +8997,14 @@
       <c r="A19" s="67" t="s">
         <v>114</v>
       </c>
-      <c r="B19" s="260" t="s">
+      <c r="B19" s="279" t="s">
         <v>48</v>
       </c>
-      <c r="C19" s="261"/>
+      <c r="C19" s="280"/>
     </row>
     <row r="20" spans="1:12" ht="39" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="253"/>
-      <c r="B20" s="268" t="s">
+      <c r="A20" s="276"/>
+      <c r="B20" s="285" t="s">
         <v>27</v>
       </c>
       <c r="C20" s="36" t="s">
@@ -9012,22 +9012,22 @@
       </c>
     </row>
     <row r="21" spans="1:12" ht="39" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="254"/>
-      <c r="B21" s="269"/>
+      <c r="A21" s="274"/>
+      <c r="B21" s="265"/>
       <c r="C21" s="37" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="39" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="254"/>
-      <c r="B22" s="270"/>
+      <c r="A22" s="274"/>
+      <c r="B22" s="286"/>
       <c r="C22" s="39" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="39" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="254"/>
-      <c r="B23" s="263" t="s">
+      <c r="A23" s="274"/>
+      <c r="B23" s="282" t="s">
         <v>32</v>
       </c>
       <c r="C23" s="36" t="s">
@@ -9035,22 +9035,22 @@
       </c>
     </row>
     <row r="24" spans="1:12" ht="39" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="254"/>
-      <c r="B24" s="271"/>
+      <c r="A24" s="274"/>
+      <c r="B24" s="287"/>
       <c r="C24" s="37" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="39" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="254"/>
-      <c r="B25" s="264"/>
+      <c r="A25" s="274"/>
+      <c r="B25" s="283"/>
       <c r="C25" s="38" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="39" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="254"/>
-      <c r="B26" s="266" t="s">
+      <c r="A26" s="274"/>
+      <c r="B26" s="262" t="s">
         <v>39</v>
       </c>
       <c r="C26" s="37" t="s">
@@ -9058,70 +9058,70 @@
       </c>
     </row>
     <row r="27" spans="1:12" ht="39" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="254"/>
-      <c r="B27" s="266"/>
+      <c r="A27" s="274"/>
+      <c r="B27" s="262"/>
       <c r="C27" s="37" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="39" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="254"/>
-      <c r="B28" s="266"/>
+      <c r="A28" s="274"/>
+      <c r="B28" s="262"/>
       <c r="C28" s="37" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="39" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="254"/>
-      <c r="B29" s="266"/>
+      <c r="A29" s="274"/>
+      <c r="B29" s="262"/>
       <c r="C29" s="37" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="39" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="254"/>
-      <c r="B30" s="266"/>
+      <c r="A30" s="274"/>
+      <c r="B30" s="262"/>
       <c r="C30" s="40" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="39" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="254"/>
-      <c r="B31" s="266"/>
+      <c r="A31" s="274"/>
+      <c r="B31" s="262"/>
       <c r="C31" s="37" t="s">
         <v>95</v>
       </c>
       <c r="D31" s="102" t="s">
         <v>49</v>
       </c>
-      <c r="G31" s="272" t="s">
+      <c r="G31" s="253" t="s">
         <v>98</v>
       </c>
-      <c r="H31" s="273"/>
-      <c r="I31" s="273"/>
-      <c r="J31" s="274"/>
+      <c r="H31" s="254"/>
+      <c r="I31" s="254"/>
+      <c r="J31" s="255"/>
       <c r="K31" s="56"/>
       <c r="L31" s="56"/>
     </row>
     <row r="32" spans="1:12" ht="39" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="254"/>
-      <c r="B32" s="266"/>
+      <c r="A32" s="274"/>
+      <c r="B32" s="262"/>
       <c r="C32" s="37" t="s">
         <v>94</v>
       </c>
       <c r="D32" s="102" t="s">
         <v>49</v>
       </c>
-      <c r="G32" s="275"/>
-      <c r="H32" s="276"/>
-      <c r="I32" s="276"/>
-      <c r="J32" s="277"/>
+      <c r="G32" s="256"/>
+      <c r="H32" s="257"/>
+      <c r="I32" s="257"/>
+      <c r="J32" s="258"/>
       <c r="K32" s="56"/>
       <c r="L32" s="56"/>
     </row>
     <row r="33" spans="1:3" ht="39" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="255"/>
-      <c r="B33" s="267"/>
+      <c r="A33" s="275"/>
+      <c r="B33" s="263"/>
       <c r="C33" s="41" t="s">
         <v>53</v>
       </c>
@@ -9131,14 +9131,14 @@
       <c r="A35" s="67" t="s">
         <v>109</v>
       </c>
-      <c r="B35" s="260" t="s">
+      <c r="B35" s="279" t="s">
         <v>54</v>
       </c>
-      <c r="C35" s="261"/>
+      <c r="C35" s="280"/>
     </row>
     <row r="36" spans="1:3" ht="28.15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="253"/>
-      <c r="B36" s="258" t="s">
+      <c r="A36" s="276"/>
+      <c r="B36" s="264" t="s">
         <v>27</v>
       </c>
       <c r="C36" s="36" t="s">
@@ -9146,21 +9146,21 @@
       </c>
     </row>
     <row r="37" spans="1:3" ht="28.15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="254"/>
-      <c r="B37" s="269"/>
+      <c r="A37" s="274"/>
+      <c r="B37" s="265"/>
       <c r="C37" s="37" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="28.15" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="254"/>
-      <c r="B38" s="259"/>
+      <c r="A38" s="274"/>
+      <c r="B38" s="266"/>
       <c r="C38" s="57" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="28.15" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="254"/>
+      <c r="A39" s="274"/>
       <c r="B39" s="42" t="s">
         <v>32</v>
       </c>
@@ -9169,8 +9169,8 @@
       </c>
     </row>
     <row r="40" spans="1:3" ht="28.15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="254"/>
-      <c r="B40" s="256" t="s">
+      <c r="A40" s="274"/>
+      <c r="B40" s="277" t="s">
         <v>39</v>
       </c>
       <c r="C40" s="36" t="s">
@@ -9178,8 +9178,8 @@
       </c>
     </row>
     <row r="41" spans="1:3" ht="38.450000000000003" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="255"/>
-      <c r="B41" s="257"/>
+      <c r="A41" s="275"/>
+      <c r="B41" s="278"/>
       <c r="C41" s="39" t="s">
         <v>99</v>
       </c>
@@ -9189,14 +9189,14 @@
       <c r="A43" s="67" t="s">
         <v>108</v>
       </c>
-      <c r="B43" s="260" t="s">
+      <c r="B43" s="279" t="s">
         <v>58</v>
       </c>
-      <c r="C43" s="261"/>
+      <c r="C43" s="280"/>
     </row>
     <row r="44" spans="1:3" ht="24" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="253"/>
-      <c r="B44" s="258" t="s">
+      <c r="A44" s="276"/>
+      <c r="B44" s="264" t="s">
         <v>27</v>
       </c>
       <c r="C44" s="36" t="s">
@@ -9204,14 +9204,14 @@
       </c>
     </row>
     <row r="45" spans="1:3" ht="24" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="254"/>
-      <c r="B45" s="259"/>
+      <c r="A45" s="274"/>
+      <c r="B45" s="266"/>
       <c r="C45" s="39" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="24" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="254"/>
+      <c r="A46" s="274"/>
       <c r="B46" s="42" t="s">
         <v>32</v>
       </c>
@@ -9220,8 +9220,8 @@
       </c>
     </row>
     <row r="47" spans="1:3" ht="24" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="254"/>
-      <c r="B47" s="256" t="s">
+      <c r="A47" s="274"/>
+      <c r="B47" s="277" t="s">
         <v>39</v>
       </c>
       <c r="C47" s="36" t="s">
@@ -9229,22 +9229,14 @@
       </c>
     </row>
     <row r="48" spans="1:3" ht="24" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="255"/>
-      <c r="B48" s="257"/>
+      <c r="A48" s="275"/>
+      <c r="B48" s="278"/>
       <c r="C48" s="39" t="s">
         <v>106</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="G31:J32"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B26:B33"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="A7:A17"/>
-    <mergeCell ref="A20:A33"/>
-    <mergeCell ref="A36:A41"/>
     <mergeCell ref="A44:A48"/>
     <mergeCell ref="B40:B41"/>
     <mergeCell ref="B44:B45"/>
@@ -9258,6 +9250,14 @@
     <mergeCell ref="B14:B17"/>
     <mergeCell ref="B20:B22"/>
     <mergeCell ref="B23:B25"/>
+    <mergeCell ref="G31:J32"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B26:B33"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="A7:A17"/>
+    <mergeCell ref="A20:A33"/>
+    <mergeCell ref="A36:A41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
